--- a/workbooks/IBCS Charts - Simple Variants Only.xlsx
+++ b/workbooks/IBCS Charts - Simple Variants Only.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfphi\AppData\Local\Temp\tmpb0b2jdi6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfphi\AppData\Local\Temp\tmpppeqwsq8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5637F9F7-4B3A-4691-9FB1-E8D82489FBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0A60AAC-2AE9-4E81-835D-0D0CB0E9AC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{01E63CBE-97A9-4EDA-ACA9-F13F63FCE299}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{6C7D07E1-1817-4BE5-9475-88B0562C528C}"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{C3DE9EBB-C6F9-4CF2-8FED-461446FACC6A}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{25C31928-BB6B-4164-BC33-2AE4DED3AFB3}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{C69DBDF1-D6C1-4B86-A05B-A72F33ABF388}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{C1DF028C-DA3E-4BEE-928C-D20662084CD9}">
       <text>
         <r>
           <rPr>
@@ -96,7 +96,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{431A308F-05AF-4591-809E-840DF026EF9F}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{0D47C361-8E0C-4BC6-B4B4-A5CC62AC50E5}">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{8FA61B8B-16E2-4F02-A944-0F12906C36A9}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{12100447-CFC9-46CA-9F77-5B0543D53F5E}">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{4A20A366-2349-48B6-8625-1B0210621BDC}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{E71646C5-5AB1-4F0B-9730-7A4EBDA51E52}">
       <text>
         <r>
           <rPr>
@@ -148,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C6572D00-419D-49D1-883B-2DC74E4E722B}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B3A37653-BBA0-4C01-80C2-B3BEE5EA002C}">
       <text>
         <r>
           <rPr>
@@ -172,7 +172,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{D4631ED8-0226-4EF7-A452-60532D9BF0AF}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{DB87F3C0-2A6E-48C1-9D8B-FC2148FE947B}">
       <text>
         <r>
           <rPr>
@@ -186,7 +186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F2D99917-CA4B-4D21-A998-0D059E45F7B5}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{AC93486F-CA5E-4829-9887-C07C702CAD52}">
       <text>
         <r>
           <rPr>
@@ -210,7 +210,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{381C8A8A-9314-4A69-B97F-5CDDE7145AC0}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{1FA6BDB5-E170-46C5-935B-477EA5110D5D}">
       <text>
         <r>
           <rPr>
@@ -224,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{27EFCCD8-69EA-4C7B-86C2-6425DC07E524}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{791FB515-A5DB-4C47-B88F-3A289F56D36D}">
       <text>
         <r>
           <rPr>
@@ -1331,7 +1331,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{90ABC47B-0D77-4D7E-93F2-46304D7070A9}</c15:txfldGUID>
+                      <c15:txfldGUID>{5C107424-D7A1-4E57-8730-FE5AF6C9F380}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1344,7 +1344,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000002-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1404,7 +1404,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{438F2343-F8CF-4E28-8B7D-65B2DD5EE618}</c15:txfldGUID>
+                      <c15:txfldGUID>{F6224530-751C-4DBB-94CF-0CDDD5365027}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1417,7 +1417,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000003-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1477,7 +1477,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{60A17F32-EB5C-43D6-860E-1DB582189EB8}</c15:txfldGUID>
+                      <c15:txfldGUID>{D10096A7-F458-4DB4-828F-FCF9789C8ADD}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1490,7 +1490,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000004-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1550,7 +1550,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4C320711-0962-4C99-81C0-B490E4EDC8AE}</c15:txfldGUID>
+                      <c15:txfldGUID>{C903E480-C897-4A41-B20A-B036A05D00C3}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1563,7 +1563,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000005-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1651,7 +1651,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{00000001-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1735,7 +1735,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3C641D1E-47D6-4AED-AEA1-17E28450240B}</c15:txfldGUID>
+                      <c15:txfldGUID>{688C9667-E3C4-40E7-906D-2090C8FD188C}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1748,7 +1748,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000007-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1808,7 +1808,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2F2995B3-4E12-4F8B-8847-0E8C2730967E}</c15:txfldGUID>
+                      <c15:txfldGUID>{1199C4C3-D9B9-4D34-9851-5401A7C2E5FD}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1821,7 +1821,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000008-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1881,7 +1881,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EC047ECC-5341-4CB5-8470-C2633D0C5B4F}</c15:txfldGUID>
+                      <c15:txfldGUID>{C93577A5-9874-46CB-8C7A-A0A0E2C0073C}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1894,7 +1894,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000009-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1954,7 +1954,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7E665335-5B22-4F79-8FB2-CB45C75C4157}</c15:txfldGUID>
+                      <c15:txfldGUID>{D04BAF8A-5ABD-4036-994F-83C5E1B90409}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1967,7 +1967,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000000A-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2055,7 +2055,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{00000006-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2136,7 +2136,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DB2E8CD3-626A-455B-BA63-DE0939000092}</c15:txfldGUID>
+                      <c15:txfldGUID>{C15B5D1C-BFDE-4334-B3E6-9675DBB56637}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2146,7 +2146,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000000C-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2203,7 +2203,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CAECF380-A156-4118-89FB-598132DC69E6}</c15:txfldGUID>
+                      <c15:txfldGUID>{03B4A061-D2E0-4131-A95B-51D91086B843}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2213,7 +2213,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000000D-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2273,7 +2273,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8C5DE648-F736-4424-9060-964C7E2146FF}</c15:txfldGUID>
+                      <c15:txfldGUID>{F7D56869-7800-4AC1-85D4-E13BE88122FF}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2286,7 +2286,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000000E-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2346,7 +2346,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2901D89C-2244-4FD9-ACFA-541B077DE354}</c15:txfldGUID>
+                      <c15:txfldGUID>{F4B762FF-FB3E-479F-ADF8-82E62CB724A2}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2359,7 +2359,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000000F-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2447,7 +2447,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{0000000B-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2531,7 +2531,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7A6A1D9B-876E-4C6C-989C-270162BCEC39}</c15:txfldGUID>
+                      <c15:txfldGUID>{31ABE644-19EF-4897-B608-B84D5F6CAC49}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2544,7 +2544,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000011-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2604,7 +2604,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8D6D6E29-23CB-44E6-B5EB-9FCE4FCDA63B}</c15:txfldGUID>
+                      <c15:txfldGUID>{61A0F6F2-FF41-4538-8CC7-F552515D0CDD}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2617,7 +2617,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000012-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2677,7 +2677,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0B71E82C-BDB9-40A5-BC47-024C12CE6220}</c15:txfldGUID>
+                      <c15:txfldGUID>{0755F404-95BB-451E-A76D-844C2C56001C}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2690,7 +2690,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000013-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2750,7 +2750,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F4D3DB24-0A8E-4553-8A18-992CCAA09876}</c15:txfldGUID>
+                      <c15:txfldGUID>{98E433F6-84B0-41D4-B8DD-2FF57A55CB65}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2763,7 +2763,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000014-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2851,7 +2851,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{00000010-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2935,7 +2935,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{92E8B446-2379-447B-A487-EDA68EBEB286}</c15:txfldGUID>
+                      <c15:txfldGUID>{5ED2C10A-DC12-425C-BCA8-0A4BDB0CBA01}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2948,7 +2948,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000016-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3008,7 +3008,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{68E22D13-78D4-4161-813D-739DF28979DE}</c15:txfldGUID>
+                      <c15:txfldGUID>{2D4AF2A3-6A2B-4104-9677-5E4621EA6C45}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3021,7 +3021,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000017-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3081,7 +3081,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FE0B4DAE-857F-45B8-984E-6E365D48530B}</c15:txfldGUID>
+                      <c15:txfldGUID>{545812AC-4D25-4615-9586-AE124BFD82F1}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3094,7 +3094,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000018-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3154,7 +3154,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{67774C51-5256-4B76-B7F0-68EBFB9815EB}</c15:txfldGUID>
+                      <c15:txfldGUID>{A2CF0B88-C29C-4717-AA82-DFE8A2D578A0}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3167,7 +3167,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{00000019-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3255,7 +3255,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000015-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{00000015-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3269,8 +3269,8 @@
         </c:dLbls>
         <c:gapWidth val="44"/>
         <c:overlap val="100"/>
-        <c:axId val="457174272"/>
-        <c:axId val="376514384"/>
+        <c:axId val="1047514832"/>
+        <c:axId val="963967120"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3359,7 +3359,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{307AAB83-D59D-47CE-8CDD-023293982471}</c15:txfldGUID>
+                      <c15:txfldGUID>{E5AF9FA8-A6E4-4BE0-997E-558B8799BB7F}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3372,7 +3372,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000001B-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3429,7 +3429,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{371479C0-D1AB-4041-B83E-C5BE34B17B18}</c15:txfldGUID>
+                      <c15:txfldGUID>{7B15D48C-94C1-4CEB-97DE-7C4A7FB66A4F}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3442,7 +3442,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000001C-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3499,7 +3499,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F70E7484-BC23-4B12-85DE-049902231517}</c15:txfldGUID>
+                      <c15:txfldGUID>{CDEE71CD-22B3-42BC-BBF8-F043E04713D4}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3512,7 +3512,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000001D-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3569,7 +3569,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2A287C5E-5CD3-4886-95F4-4C1D0EAB1F4B}</c15:txfldGUID>
+                      <c15:txfldGUID>{41C6C287-7DB6-425A-90BA-EC607121B023}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3582,7 +3582,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-5419-4F4B-B8E1-AF14121A5CE7}"/>
+                  <c16:uniqueId val="{0000001E-60F7-4A81-BBA9-8654F4D20E73}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3668,7 +3668,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001A-5419-4F4B-B8E1-AF14121A5CE7}"/>
+              <c16:uniqueId val="{0000001A-60F7-4A81-BBA9-8654F4D20E73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3682,11 +3682,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="457174272"/>
-        <c:axId val="376514384"/>
+        <c:axId val="1047514832"/>
+        <c:axId val="963967120"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="457174272"/>
+        <c:axId val="1047514832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3710,7 +3710,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376514384"/>
+        <c:crossAx val="963967120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3718,7 +3718,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="376514384"/>
+        <c:axId val="963967120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.1776251226692835"/>
@@ -3752,7 +3752,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="457174272"/>
+        <c:crossAx val="1047514832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3922,7 +3922,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{950C891C-4D16-453B-8219-78016B6C6A7F}</c15:txfldGUID>
+                      <c15:txfldGUID>{DB3529ED-4E03-44DE-92E6-914731F94FDE}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3935,7 +3935,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000002-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3995,7 +3995,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3E0A1EB1-633E-4133-8A67-47134FC88CBA}</c15:txfldGUID>
+                      <c15:txfldGUID>{D57D5B65-3980-4D37-B7A9-008EC72C42B5}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4008,7 +4008,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000003-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4068,7 +4068,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7E6B636F-BC76-4C11-988C-62E357D1BFD2}</c15:txfldGUID>
+                      <c15:txfldGUID>{B78E379A-3AE6-4489-92D2-BC16BDA6F157}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4081,7 +4081,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000004-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4141,7 +4141,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EF03E60D-D084-4E9D-9922-7D31CD722F13}</c15:txfldGUID>
+                      <c15:txfldGUID>{591A8149-C8EA-4E10-8407-E0FACDFAFC3E}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4154,7 +4154,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000005-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4214,7 +4214,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7024D311-2825-4608-9CC1-275A63545E0D}</c15:txfldGUID>
+                      <c15:txfldGUID>{47C33C39-8445-41AD-AEFE-E0CB8124E2CA}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4227,7 +4227,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000006-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4287,7 +4287,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{15A4205B-87EB-4EA8-ABE9-4BD22B1D6AEC}</c15:txfldGUID>
+                      <c15:txfldGUID>{8DEADD34-BB96-4466-8D30-BF245A6FC3DF}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4300,7 +4300,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000007-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4360,7 +4360,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{96C2FEF4-2931-413E-B244-33F92A3FA458}</c15:txfldGUID>
+                      <c15:txfldGUID>{5EF9C8E8-268C-4D70-A2EC-276FE39B1C6A}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4373,7 +4373,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000008-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4433,7 +4433,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BCE703EB-1D71-4D85-9C85-F1B21CA9194B}</c15:txfldGUID>
+                      <c15:txfldGUID>{9D01E557-8F68-43EE-A724-62418BD91629}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4446,7 +4446,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000009-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4506,7 +4506,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6E0B7896-FF9E-4602-A7BE-C7EDACEA6677}</c15:txfldGUID>
+                      <c15:txfldGUID>{80B2AE68-FA88-495A-9B97-5280FC456388}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4519,7 +4519,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000A-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4579,7 +4579,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A5F21E15-9FDA-49A2-AE86-3326D4F446BA}</c15:txfldGUID>
+                      <c15:txfldGUID>{64AB48DF-3410-4953-9E70-C6F45E972FE5}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4592,7 +4592,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000B-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4652,7 +4652,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D2E407EC-18CE-4265-918D-015ECBA41419}</c15:txfldGUID>
+                      <c15:txfldGUID>{F5B1B03F-938F-4DDC-82BF-AAC233DE0DB7}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4665,7 +4665,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000C-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4722,7 +4722,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{65AE55AE-BDC7-41A5-8B9D-16DAC97E7EBE}</c15:txfldGUID>
+                      <c15:txfldGUID>{3CC8863E-D665-4F24-96E0-53F5AB0241AA}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4732,7 +4732,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000D-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4789,7 +4789,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3F0E0340-4061-4581-975F-7EEB7E0DE7BF}</c15:txfldGUID>
+                      <c15:txfldGUID>{C11285AF-7F40-4232-9D48-D9830D3FA0FA}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4799,7 +4799,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000E-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4859,7 +4859,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E8E5BE86-91D7-416B-A0E7-301070A5F7D1}</c15:txfldGUID>
+                      <c15:txfldGUID>{13A93B60-F62A-4A69-B1EA-83FB4A46CEA4}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4872,7 +4872,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000000F-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4932,7 +4932,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5A277ABA-F971-46BD-913A-3BAF804616B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{51C1782B-2373-461C-AD91-5B2941AB6A55}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4945,7 +4945,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000010-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5005,7 +5005,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D73FB50F-1AB5-46D7-85EF-C5EE937A884D}</c15:txfldGUID>
+                      <c15:txfldGUID>{4B0D0EA5-9D4E-4D36-9742-892BF1E35FAC}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5018,7 +5018,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000011-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5078,7 +5078,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C02F0BE9-AEF4-4005-A708-3463E6594E92}</c15:txfldGUID>
+                      <c15:txfldGUID>{2ABB4BB2-A787-4C3F-A1D8-F40C8B6FBC09}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5091,7 +5091,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000012-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5151,7 +5151,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3C2E5D2E-62C3-467B-A567-BE960C534CC5}</c15:txfldGUID>
+                      <c15:txfldGUID>{A8C0C122-B7FB-4915-AF6E-7D9A64E0C86A}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5164,7 +5164,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000013-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5224,7 +5224,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9EA43145-BFCE-4133-8117-C91AFE7FD3A9}</c15:txfldGUID>
+                      <c15:txfldGUID>{BD0B86B7-ABF7-4093-BAAB-621B841D5321}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5237,7 +5237,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000014-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5415,7 +5415,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA8D-461C-A538-46D22F1B0BA2}"/>
+              <c16:uniqueId val="{00000001-125D-4136-8E7E-31D06DE5190E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5499,7 +5499,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{638D555F-245E-46CB-A6A7-7AE6075F907E}</c15:txfldGUID>
+                      <c15:txfldGUID>{551B504A-9866-453A-8336-3ECBE8D4CD14}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5512,7 +5512,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000016-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5572,7 +5572,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{854F4AFA-F6A4-478A-A9A6-62371A76B42B}</c15:txfldGUID>
+                      <c15:txfldGUID>{43D4A03E-8847-4B54-BEB8-DAA713DFEA75}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5585,7 +5585,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000017-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5645,7 +5645,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{422A6B62-2B8E-4F62-AC08-72BD69D239A9}</c15:txfldGUID>
+                      <c15:txfldGUID>{970853A5-0629-40C3-9131-0C506756E771}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5658,7 +5658,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000018-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5718,7 +5718,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4DA5FC97-D711-43DE-A7F6-F67D6E211069}</c15:txfldGUID>
+                      <c15:txfldGUID>{8BE56913-F8D4-4824-B3D5-FAE9A394C3F7}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5731,7 +5731,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000019-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5791,7 +5791,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DE28FADF-3DDD-4421-BEF3-B29F2EEC4DDF}</c15:txfldGUID>
+                      <c15:txfldGUID>{9E7B9C26-3A82-4C45-91D5-6D0A1295FF40}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5804,7 +5804,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001A-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5864,7 +5864,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{15E051EB-8A3E-4F7D-9709-745C034B37F9}</c15:txfldGUID>
+                      <c15:txfldGUID>{0B6480A2-8BE5-4E74-902D-F8449AC81262}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5877,7 +5877,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001B-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5937,7 +5937,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E01FF9B9-BBE5-41F5-A9F5-D5A88A3085B6}</c15:txfldGUID>
+                      <c15:txfldGUID>{2DA4B7F2-6390-46E3-906C-56DE5CEA5447}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5950,7 +5950,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001C-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6010,7 +6010,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5053E20D-B204-44F5-B7BC-D6AF347F3FE9}</c15:txfldGUID>
+                      <c15:txfldGUID>{5C4D0510-DD5D-45A2-A286-C4B9B3ADF18E}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6023,7 +6023,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001D-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6083,7 +6083,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{795F137D-67D2-4619-BF63-A43CF69356A6}</c15:txfldGUID>
+                      <c15:txfldGUID>{52273E51-E9D8-4796-A144-CD1D139A3CA6}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6096,7 +6096,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001E-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6156,7 +6156,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{08671D1E-876E-45C2-B62C-7534C16C0F63}</c15:txfldGUID>
+                      <c15:txfldGUID>{485F47CC-9F71-41A7-896A-D99DBFB5E7FB}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6169,7 +6169,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000001F-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6229,7 +6229,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{38CA57B3-B555-4AB0-A1EC-8971B789DEBE}</c15:txfldGUID>
+                      <c15:txfldGUID>{7BB7E5B5-E3FF-4DC7-96EF-D5C0FFB45971}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6242,7 +6242,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000020-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6302,7 +6302,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9BD1D2C7-3BBA-4C2E-A3BF-307D2075275B}</c15:txfldGUID>
+                      <c15:txfldGUID>{647C4C02-C3D1-4541-B10E-27FD7F1CA0CD}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6315,7 +6315,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000021-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6372,7 +6372,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D39C1B88-B058-42C7-A227-A96FFC56424A}</c15:txfldGUID>
+                      <c15:txfldGUID>{A17987F0-7B8F-4683-9A33-22916917DBB5}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6382,7 +6382,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000022-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6442,7 +6442,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{98CD5181-F976-4D07-98F6-0E9D8FE8F096}</c15:txfldGUID>
+                      <c15:txfldGUID>{D5219F4B-B291-4B05-881C-76A902E23494}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6455,7 +6455,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000023-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6515,7 +6515,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6591F89A-8DC8-49FA-8749-07C5D1F0C328}</c15:txfldGUID>
+                      <c15:txfldGUID>{B1451787-ED7D-4D05-9A07-D1ED1BEC2083}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6528,7 +6528,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000024-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6588,7 +6588,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7ECACC21-0E4A-451A-B20D-6F3B559B2706}</c15:txfldGUID>
+                      <c15:txfldGUID>{18445164-93F4-4898-A2CE-E8D203FB10DB}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6601,7 +6601,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000025-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6661,7 +6661,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A76AD413-E9A5-44FB-A453-1E3EF35119A2}</c15:txfldGUID>
+                      <c15:txfldGUID>{8C836500-EDC8-4F6A-B84D-C35991C3238E}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6674,7 +6674,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000026-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6731,7 +6731,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{54D4D538-75F8-4744-8C24-4ECB95AFEEB9}</c15:txfldGUID>
+                      <c15:txfldGUID>{9C8F88E3-6833-4E92-830C-7F77195DDFFC}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6741,7 +6741,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000027-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6801,7 +6801,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9514F1EF-BF1F-477C-A042-D1A7A3B3C7FC}</c15:txfldGUID>
+                      <c15:txfldGUID>{1E3BCA9E-996E-4FD4-AAD7-D5401DFA208D}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6814,7 +6814,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000028-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6992,7 +6992,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000015-DA8D-461C-A538-46D22F1B0BA2}"/>
+              <c16:uniqueId val="{00000015-125D-4136-8E7E-31D06DE5190E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7076,7 +7076,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7402A2DC-0467-4861-B038-05B4855CC774}</c15:txfldGUID>
+                      <c15:txfldGUID>{5400E5F1-7585-46C0-AD69-6C9CFE8AEFCF}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7089,7 +7089,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002A-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7149,7 +7149,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3A741776-B4CB-4EAA-A595-FE120139AA6A}</c15:txfldGUID>
+                      <c15:txfldGUID>{446075DA-D3A2-455A-81B9-8311372FBCBF}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7162,7 +7162,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002B-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7222,7 +7222,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{01F6B8AF-A6BA-4996-90D4-943DB42B861C}</c15:txfldGUID>
+                      <c15:txfldGUID>{2666AF03-698B-4775-A8F6-84929A4C81A5}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7235,7 +7235,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002C-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7295,7 +7295,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AFFE96B8-7FC6-4ECB-BD08-58C97560E069}</c15:txfldGUID>
+                      <c15:txfldGUID>{ED24586E-0629-458F-95FB-DE146F65864E}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7308,7 +7308,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002D-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7368,7 +7368,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C52A487B-5665-408D-968D-892CC89860AB}</c15:txfldGUID>
+                      <c15:txfldGUID>{C326AACD-673A-4448-B127-43186210A894}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7381,7 +7381,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002E-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7441,7 +7441,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5F89C714-CD33-4ACA-985F-549E52BC2DA5}</c15:txfldGUID>
+                      <c15:txfldGUID>{6BD1CB06-64FD-4C1B-8DC0-43F61BD1434C}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7454,7 +7454,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000002F-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7514,7 +7514,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B367F327-E65E-4900-94DA-C9D554E191FF}</c15:txfldGUID>
+                      <c15:txfldGUID>{A0949A0C-31C8-4C42-A74F-E1CD500CD2D1}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7527,7 +7527,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000030-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7584,7 +7584,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B7BE3F61-11B7-49AC-8C24-6C4D40597DF6}</c15:txfldGUID>
+                      <c15:txfldGUID>{BF8B0E62-707D-4C60-B7E4-778776D38301}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7594,7 +7594,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000031-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7654,7 +7654,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4730100E-FA46-4FD3-B4A4-B37FD6880B62}</c15:txfldGUID>
+                      <c15:txfldGUID>{CC70767A-347B-40E5-B7F8-85B6D1A85E4D}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7667,7 +7667,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000032-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7724,7 +7724,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2A700022-DEAA-41C9-9960-68723C700D88}</c15:txfldGUID>
+                      <c15:txfldGUID>{E0ED057C-8E6D-4205-8B98-C7574C72515B}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7734,7 +7734,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000033-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7791,7 +7791,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{1CB33859-38C9-45AB-B41D-F90FECB7E798}</c15:txfldGUID>
+                      <c15:txfldGUID>{C1ABDD42-F88C-45AA-91D3-038F2A153721}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7801,7 +7801,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000034-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7861,7 +7861,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{56E85DA4-7F86-4D79-89E9-8572A548AEB4}</c15:txfldGUID>
+                      <c15:txfldGUID>{A45638BB-8FA6-464E-8432-B54680FDE5A4}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7874,7 +7874,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000035-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7931,7 +7931,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{32FEAE10-939A-497C-85B8-17FFD0DE3EA4}</c15:txfldGUID>
+                      <c15:txfldGUID>{07EBF548-C506-4CA1-BFB8-134B00C971BA}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7941,7 +7941,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000036-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8001,7 +8001,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{598637D1-A5A8-4C0F-AF82-87EF0D97E67F}</c15:txfldGUID>
+                      <c15:txfldGUID>{A70D64B6-CFCB-455A-8EE8-D5161BB3222C}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8014,7 +8014,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000037-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8074,7 +8074,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{43CD6454-EB05-4F57-856E-13EE13E883E3}</c15:txfldGUID>
+                      <c15:txfldGUID>{3BADE7BF-F929-45EF-82B9-33120A21B363}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8087,7 +8087,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000038-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8147,7 +8147,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8A77D22A-D249-4A6B-B27A-27A5D092D9EC}</c15:txfldGUID>
+                      <c15:txfldGUID>{6011EDBD-00F4-4105-9C1F-0B99D19802F2}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8160,7 +8160,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000039-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8220,7 +8220,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{68B825C3-90C9-4FE5-AF43-DAE893132586}</c15:txfldGUID>
+                      <c15:txfldGUID>{D254668C-F4F7-4DA9-B97F-937E40BAD5D1}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8233,7 +8233,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000003A-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8290,7 +8290,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2E7B0F6D-3265-417A-83E6-06CC72D58223}</c15:txfldGUID>
+                      <c15:txfldGUID>{4B72A715-97D9-4FC2-8683-07CF2A964959}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8300,7 +8300,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000003B-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8360,7 +8360,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{764370B2-B9FD-483F-8C12-27EA0FD6BF87}</c15:txfldGUID>
+                      <c15:txfldGUID>{99CD8843-C9E3-4058-A9ED-04787D467EFD}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8373,7 +8373,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000003C-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8551,7 +8551,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000029-DA8D-461C-A538-46D22F1B0BA2}"/>
+              <c16:uniqueId val="{00000029-125D-4136-8E7E-31D06DE5190E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8638,7 +8638,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6B1871A9-6F9B-4D51-BC8E-6BEF87E3A39F}</c15:txfldGUID>
+                      <c15:txfldGUID>{648E0BE6-0945-470F-9B21-E132CAC30495}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8651,7 +8651,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000003E-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8709,7 +8709,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{02AB5656-DB58-4811-AA16-94CEF651E2DD}</c15:txfldGUID>
+                      <c15:txfldGUID>{90868870-47F6-44D4-8763-E06FA800030D}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8722,7 +8722,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000003F-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8780,7 +8780,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FB00E180-B0E2-4420-B314-523A2D6A4534}</c15:txfldGUID>
+                      <c15:txfldGUID>{83B7FD69-3BE6-495E-ABC3-6AB8B61CC287}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8793,7 +8793,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000040-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000040-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8851,7 +8851,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8F189584-B677-47EE-B705-CD6BC1061A70}</c15:txfldGUID>
+                      <c15:txfldGUID>{655A6C1D-D71F-4E15-8FA8-181EE2BE807C}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8864,7 +8864,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000041-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8922,7 +8922,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FCE5081F-02F5-41E6-AADF-706A838CAF9A}</c15:txfldGUID>
+                      <c15:txfldGUID>{204F87EA-81C1-409A-A574-49E1C90C92FF}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8935,7 +8935,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000042-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8993,7 +8993,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{76759369-B010-4064-957B-5AF29DAA3978}</c15:txfldGUID>
+                      <c15:txfldGUID>{A41AEBA9-8F88-4F5E-A7FC-81EF9FEEFA41}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9006,7 +9006,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000043-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9064,7 +9064,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DBE1809F-1439-4B86-A499-D3CD4E3DB242}</c15:txfldGUID>
+                      <c15:txfldGUID>{5689B76B-17F8-4745-9D59-8025F7D23482}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9077,7 +9077,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000044-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9135,7 +9135,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8E9FAB98-EC3B-4AA6-8F8E-10AF721F9E9B}</c15:txfldGUID>
+                      <c15:txfldGUID>{3CA01EE8-8973-49E6-82A0-EA3E47A99074}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9148,7 +9148,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000045-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9206,7 +9206,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BE6028EC-CAF9-4C64-B035-FE8C28B4BAA2}</c15:txfldGUID>
+                      <c15:txfldGUID>{8A68B6EA-681A-44D6-AF73-A89EC308F61C}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9219,7 +9219,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000046-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9277,7 +9277,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{12E89A68-BF9E-42BB-A682-331A38ECC3A2}</c15:txfldGUID>
+                      <c15:txfldGUID>{387CED6A-7A74-4B63-965D-E61906E6BCAF}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9290,7 +9290,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000047-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000047-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9348,7 +9348,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C6D7DE31-4F6C-4B8E-A951-F52AC1AD1614}</c15:txfldGUID>
+                      <c15:txfldGUID>{BDDCB932-7DE9-4781-BDF3-B2A14D136DB4}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9361,7 +9361,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000048-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9419,7 +9419,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{03C83F8E-1FEA-404A-BED3-6E4F9CE71653}</c15:txfldGUID>
+                      <c15:txfldGUID>{7C7618C9-C140-4F5A-A7AA-A853A6E20E09}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9432,7 +9432,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000049-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9490,7 +9490,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A26C8ACF-62E3-4CEF-88A3-79AC7FC5798F}</c15:txfldGUID>
+                      <c15:txfldGUID>{DFDFF4B6-8D93-4738-9806-9057E53C6B90}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9503,7 +9503,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004A-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9561,7 +9561,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{98B6DCEF-91A7-409F-8D18-5F80DE63DC71}</c15:txfldGUID>
+                      <c15:txfldGUID>{A955CA77-D453-411E-9D79-D745D2D94DB4}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9574,7 +9574,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004B-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9632,7 +9632,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9020D600-5DF9-417B-9292-0BFA628AF3C7}</c15:txfldGUID>
+                      <c15:txfldGUID>{4E6F187D-8382-4A2F-A259-28881CF153A4}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9645,7 +9645,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004C-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9703,7 +9703,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7C54DF19-860A-4381-92A9-FA100063FBD5}</c15:txfldGUID>
+                      <c15:txfldGUID>{59DDC589-A1A6-4760-AE75-988F495A0F8F}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9716,7 +9716,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004D-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9774,7 +9774,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D73A2DC7-5F9E-4172-A48E-E62611F98D95}</c15:txfldGUID>
+                      <c15:txfldGUID>{A433E028-EB3E-4C37-8797-FC1976F8654C}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9787,7 +9787,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004E-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9845,7 +9845,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E8A1D09E-F318-4F9C-B22E-95836772365B}</c15:txfldGUID>
+                      <c15:txfldGUID>{0F9A258D-771A-4C71-B052-B1B10C098EBD}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9858,7 +9858,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004F-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{0000004F-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9916,7 +9916,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{82ADF816-10E6-45C0-A712-CEC3A3981A05}</c15:txfldGUID>
+                      <c15:txfldGUID>{67247598-C8EE-4FC5-9143-45D050BD7B73}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9929,7 +9929,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000050-DA8D-461C-A538-46D22F1B0BA2}"/>
+                  <c16:uniqueId val="{00000050-125D-4136-8E7E-31D06DE5190E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10100,7 +10100,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000003D-DA8D-461C-A538-46D22F1B0BA2}"/>
+              <c16:uniqueId val="{0000003D-125D-4136-8E7E-31D06DE5190E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10114,11 +10114,11 @@
         </c:dLbls>
         <c:gapWidth val="26"/>
         <c:overlap val="100"/>
-        <c:axId val="1100614240"/>
-        <c:axId val="1018506224"/>
+        <c:axId val="1701264896"/>
+        <c:axId val="1604276176"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1100614240"/>
+        <c:axId val="1701264896"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -10142,7 +10142,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018506224"/>
+        <c:crossAx val="1604276176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10150,7 +10150,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018506224"/>
+        <c:axId val="1604276176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0080645161290323"/>
@@ -10184,7 +10184,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1100614240"/>
+        <c:crossAx val="1701264896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10398,7 +10398,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-433B-474F-9E12-8599430F2AB6}"/>
+              <c16:uniqueId val="{00000007-4B90-43A6-9DED-8B0FFA6B2726}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10447,7 +10447,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-433B-474F-9E12-8599430F2AB6}"/>
+                <c16:uniqueId val="{00000009-4B90-43A6-9DED-8B0FFA6B2726}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10473,7 +10473,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000A-433B-474F-9E12-8599430F2AB6}"/>
+                <c16:uniqueId val="{0000000A-4B90-43A6-9DED-8B0FFA6B2726}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10499,7 +10499,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-433B-474F-9E12-8599430F2AB6}"/>
+                <c16:uniqueId val="{0000000B-4B90-43A6-9DED-8B0FFA6B2726}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10528,7 +10528,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{1C5CEE93-C82E-45C4-AC0E-98D383BF6893}</c15:txfldGUID>
+                      <c15:txfldGUID>{18A2FCF0-ED9D-4EF9-AD94-6A6670FBAE6D}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10541,7 +10541,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000C-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10569,7 +10569,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4801E7A8-3950-4515-8CE7-3C66827D4D9E}</c15:txfldGUID>
+                      <c15:txfldGUID>{D2E41518-84C9-4A9A-96D4-D4214634AB97}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10582,7 +10582,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000D-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10610,7 +10610,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{62420D52-302A-4950-94DC-A0E7058DBAD5}</c15:txfldGUID>
+                      <c15:txfldGUID>{62666FB1-6AC6-4DD7-8D32-CE74754C6104}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10623,7 +10623,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000E-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10651,7 +10651,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0A4EA2AB-8DE3-4854-9999-4B080FC0415B}</c15:txfldGUID>
+                      <c15:txfldGUID>{2C9F1D77-BDBA-4837-BA31-61093818EE3B}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10664,7 +10664,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000F-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10692,7 +10692,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{334416C0-E1AD-4F3F-9BD8-46E891E3D750}</c15:txfldGUID>
+                      <c15:txfldGUID>{DA22CCDF-10EF-483F-937C-22087358E79A}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10705,7 +10705,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000010-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10733,7 +10733,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{92043A63-1DE1-45E4-A644-66DC0A2C978D}</c15:txfldGUID>
+                      <c15:txfldGUID>{A43B8920-1944-4FE1-A662-0B3A558B00AE}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10746,7 +10746,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000011-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10774,7 +10774,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C95C4E82-07EE-49C8-BC3A-E8F7DE352231}</c15:txfldGUID>
+                      <c15:txfldGUID>{1FE409A8-058A-4CF2-B6E2-F100D4E78CFD}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10787,7 +10787,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000012-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10815,7 +10815,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2CE2FDD1-E3EB-43F6-ACAE-8920D6FBDA05}</c15:txfldGUID>
+                      <c15:txfldGUID>{1F69DD37-121B-4671-A0F2-1827AAEA0A3A}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10828,7 +10828,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000013-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10856,7 +10856,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6DA97CC7-C27A-4F97-9414-1CD85CD90459}</c15:txfldGUID>
+                      <c15:txfldGUID>{5E25A121-1564-418F-99C3-AA181FBEE3F8}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10869,7 +10869,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000014-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10897,7 +10897,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{26734116-F6BA-4103-ADC0-1E67AE84665F}</c15:txfldGUID>
+                      <c15:txfldGUID>{45536DDC-98E9-42B9-92BE-6DF0FFC1A069}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10910,7 +10910,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{00000009-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10938,7 +10938,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E1671841-4808-47D0-A38B-577A2B5ECB6E}</c15:txfldGUID>
+                      <c15:txfldGUID>{6E6A7E7F-B5CA-4004-802A-0DE79BFA4F04}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10951,7 +10951,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000A-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10979,7 +10979,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E6821E01-1B3B-47CB-847E-F831F2DBBC22}</c15:txfldGUID>
+                      <c15:txfldGUID>{498C8815-E588-4B85-A35D-2CB88601296B}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10992,7 +10992,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-433B-474F-9E12-8599430F2AB6}"/>
+                  <c16:uniqueId val="{0000000B-4B90-43A6-9DED-8B0FFA6B2726}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11125,7 +11125,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-433B-474F-9E12-8599430F2AB6}"/>
+              <c16:uniqueId val="{00000008-4B90-43A6-9DED-8B0FFA6B2726}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11139,11 +11139,11 @@
         </c:dLbls>
         <c:gapWidth val="23"/>
         <c:overlap val="76"/>
-        <c:axId val="1102675328"/>
-        <c:axId val="1018290224"/>
+        <c:axId val="1707305440"/>
+        <c:axId val="1604057296"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1102675328"/>
+        <c:axId val="1707305440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11167,7 +11167,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018290224"/>
+        <c:crossAx val="1604057296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11175,7 +11175,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018290224"/>
+        <c:axId val="1604057296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0900473933649288"/>
@@ -11209,7 +11209,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1102675328"/>
+        <c:crossAx val="1707305440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11464,7 +11464,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-36CC-44F9-8E73-6D08B2FEFA06}"/>
+              <c16:uniqueId val="{00000007-525E-4935-82BA-06B8ECB63C36}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11516,7 +11516,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{391EA1BE-605E-4CD3-8230-3E8C9EAFE4D7}</c15:txfldGUID>
+                      <c15:txfldGUID>{24F6DC45-E9DD-4898-AA91-26309FB4CC19}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11529,7 +11529,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000009-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11557,7 +11557,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9813FF28-8A01-4AAB-AAF9-C1356D3F24DB}</c15:txfldGUID>
+                      <c15:txfldGUID>{F0D4ECCB-7DDC-4A22-B5C8-E72FDEEA9F9B}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11570,7 +11570,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000A-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11598,7 +11598,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{67299F72-C759-4F51-8D01-3DD905531510}</c15:txfldGUID>
+                      <c15:txfldGUID>{AB0C14AA-F0CB-4811-9AAB-987D5090691C}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11611,7 +11611,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000B-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11639,7 +11639,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{775E178D-C16C-4923-93D6-22A0E4BFADD0}</c15:txfldGUID>
+                      <c15:txfldGUID>{58231B0C-77FC-4AAF-8190-CE7AFF5BF26C}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11652,7 +11652,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000C-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11680,7 +11680,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EFC55E85-26AF-47B7-886A-648C8E0F299C}</c15:txfldGUID>
+                      <c15:txfldGUID>{5455CAD6-4A76-4276-B802-BF38B4279C38}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11693,7 +11693,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000D-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11721,7 +11721,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0CE77DA5-3555-4108-BC4B-13AEBCAF53E2}</c15:txfldGUID>
+                      <c15:txfldGUID>{90C3D332-0BFC-45E0-BB81-1D900200B251}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11734,7 +11734,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000E-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11762,7 +11762,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A7C4A27B-55D2-4A12-B13D-8BF1B3B429AB}</c15:txfldGUID>
+                      <c15:txfldGUID>{8FAE9044-61AE-4EA7-B674-70B7A4440C63}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11775,7 +11775,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000000F-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11803,7 +11803,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{646EFF4D-4FF8-4360-8CB2-8ECBDD5E84DB}</c15:txfldGUID>
+                      <c15:txfldGUID>{30E5BC4C-6F91-41E1-BFA2-2A983A3378B6}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11816,7 +11816,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000010-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11844,7 +11844,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ADD1598E-7A6E-445E-9225-BBC9E5892632}</c15:txfldGUID>
+                      <c15:txfldGUID>{720CB497-1A73-43E4-B2A7-0C7AF4F5B810}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11857,7 +11857,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000011-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11885,7 +11885,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{19FAD846-D534-412A-92E5-48FCC9F054CF}</c15:txfldGUID>
+                      <c15:txfldGUID>{54F0F951-F780-41CF-A459-0D108A9C8F7A}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11898,7 +11898,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000012-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11926,7 +11926,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{333395E1-5B71-4C75-A824-588C37FA6AEE}</c15:txfldGUID>
+                      <c15:txfldGUID>{94924B91-EC9E-486A-955F-D9ABC3D4D6AA}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11939,7 +11939,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000013-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11967,7 +11967,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{67B32BE0-E4FB-460C-A1EA-90E15B1380E5}</c15:txfldGUID>
+                      <c15:txfldGUID>{9FBAF82D-C4B6-438B-9493-43E72E730D2B}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11980,7 +11980,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000014-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12008,7 +12008,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0CD25B05-8F64-45B0-95D7-E8CB0BA23BD7}</c15:txfldGUID>
+                      <c15:txfldGUID>{C8E1F8B7-41F4-483A-9A6F-6FFD332862DE}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12021,7 +12021,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000015-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12049,7 +12049,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{79783754-0C44-4EAE-B06A-06BC2681F6C2}</c15:txfldGUID>
+                      <c15:txfldGUID>{77D00019-9858-4293-8FD3-BDBA7EC4C935}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12062,7 +12062,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000016-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12090,7 +12090,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5BE30D18-0DB9-47E0-8466-A90ACE9D91E3}</c15:txfldGUID>
+                      <c15:txfldGUID>{06CC5AC2-62AC-4FDE-BE30-828F6EB3F137}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12103,7 +12103,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000017-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12131,7 +12131,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BA80837B-59BA-4DF0-8B2A-113499989B2C}</c15:txfldGUID>
+                      <c15:txfldGUID>{F0DB056C-57B3-4A0F-9D37-F46FF9AA1FEE}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12144,7 +12144,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000018-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12172,7 +12172,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6BD1E037-040E-410C-A572-F38E60BDE88B}</c15:txfldGUID>
+                      <c15:txfldGUID>{3AC905F1-FFC0-475D-9D63-192A370E36E9}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12185,7 +12185,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{00000019-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12213,7 +12213,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{65144796-A00A-48D0-805D-628DD24F740E}</c15:txfldGUID>
+                      <c15:txfldGUID>{29D2A7AE-C40A-492A-84FA-2D5E06644F65}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12226,7 +12226,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000001A-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12254,7 +12254,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BA5D8CFC-A482-4A09-BA91-B3C0A66F37CD}</c15:txfldGUID>
+                      <c15:txfldGUID>{87796B3A-3D09-41C3-871E-29D276B9CE8F}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12267,7 +12267,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-36CC-44F9-8E73-6D08B2FEFA06}"/>
+                  <c16:uniqueId val="{0000001B-525E-4935-82BA-06B8ECB63C36}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12442,7 +12442,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-36CC-44F9-8E73-6D08B2FEFA06}"/>
+              <c16:uniqueId val="{00000008-525E-4935-82BA-06B8ECB63C36}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12456,11 +12456,11 @@
         </c:dLbls>
         <c:gapWidth val="20"/>
         <c:overlap val="76"/>
-        <c:axId val="1103611920"/>
-        <c:axId val="1018319024"/>
+        <c:axId val="1709164560"/>
+        <c:axId val="1604091376"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1103611920"/>
+        <c:axId val="1709164560"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -12484,7 +12484,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018319024"/>
+        <c:crossAx val="1604091376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12492,10 +12492,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018319024"/>
+        <c:axId val="1604091376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="240"/>
+          <c:max val="1.095890410958904"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -12526,7 +12526,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1103611920"/>
+        <c:crossAx val="1709164560"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12780,7 +12780,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-F2C9-46E7-8EA1-430489EBE003}"/>
+              <c16:uniqueId val="{00000007-3383-41D1-9977-0A357D1962B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12814,7 +12814,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000009-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12824,7 +12824,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000A-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12852,7 +12852,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{62992E06-8513-41D7-B7C0-3F1479BDB117}</c15:txfldGUID>
+                      <c15:txfldGUID>{28228B74-0DD8-44A4-9E51-08635B3456F1}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12865,7 +12865,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000B-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12893,7 +12893,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7C1B3E18-7AE1-4041-B8BA-8995783C82E2}</c15:txfldGUID>
+                      <c15:txfldGUID>{3A79AC2E-E23F-41B4-89AC-A452E335372F}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12906,7 +12906,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000C-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12934,7 +12934,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3752A491-4A4E-4E4C-9C9E-0C8AE8527F6D}</c15:txfldGUID>
+                      <c15:txfldGUID>{1C82149F-7DCE-4C8F-9816-C71D6279E183}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12947,7 +12947,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000D-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12957,7 +12957,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000E-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12967,7 +12967,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000000F-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12977,7 +12977,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000010-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12987,7 +12987,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000011-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12997,7 +12997,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000012-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13007,7 +13007,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000013-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13017,7 +13017,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000014-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13027,7 +13027,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000015-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13037,7 +13037,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000016-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13047,7 +13047,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000017-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13075,7 +13075,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2E906F7E-734B-4001-8A5B-A2D04F345F7E}</c15:txfldGUID>
+                      <c15:txfldGUID>{A92740D2-6E18-4D91-938F-7107173D2CF6}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13088,7 +13088,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000018-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13116,7 +13116,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{27831D67-A630-4FAE-BCD7-A251ECAE7BCA}</c15:txfldGUID>
+                      <c15:txfldGUID>{AA2B8196-553D-4A28-8ABE-321C2B14ADE4}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13129,7 +13129,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000019-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13292,7 +13292,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-F2C9-46E7-8EA1-430489EBE003}"/>
+              <c16:uniqueId val="{00000008-3383-41D1-9977-0A357D1962B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13326,7 +13326,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000001B-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13336,7 +13336,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000001C-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13346,7 +13346,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000001D-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13356,7 +13356,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000001E-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13366,7 +13366,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000001F-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13394,7 +13394,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{071E190F-F3BF-4118-8F37-BC457B62666D}</c15:txfldGUID>
+                      <c15:txfldGUID>{DC9DF095-8862-4837-A14C-FEDC241FAE7F}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13407,7 +13407,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000020-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13435,7 +13435,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{71A04D3E-892E-4C71-9AC3-A87F95DDCCB3}</c15:txfldGUID>
+                      <c15:txfldGUID>{DA77B6A0-45F3-452F-AAC7-1ED49855E4E2}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13448,7 +13448,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000021-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13476,7 +13476,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A578B443-1D87-47C9-BE8B-5469DC7B82BF}</c15:txfldGUID>
+                      <c15:txfldGUID>{C349ABA0-7978-4645-91A1-5F982467F578}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13489,7 +13489,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000022-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13517,7 +13517,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CE5817FE-0453-496F-801E-24B0B7E1F5F2}</c15:txfldGUID>
+                      <c15:txfldGUID>{BBE15CCF-10E0-4A07-9BDD-E96313EFA5D1}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13530,7 +13530,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000023-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13558,7 +13558,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C6A23B5B-D4B9-4006-816F-ADA38C766077}</c15:txfldGUID>
+                      <c15:txfldGUID>{33AABF74-4B20-403B-9FA8-DD187C841457}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13571,7 +13571,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000024-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13581,7 +13581,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000025-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13591,7 +13591,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000026-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13601,7 +13601,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000027-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13611,7 +13611,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000028-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13621,7 +13621,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000029-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13631,7 +13631,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000002A-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13641,7 +13641,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000002B-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13804,7 +13804,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001A-F2C9-46E7-8EA1-430489EBE003}"/>
+              <c16:uniqueId val="{0000001A-3383-41D1-9977-0A357D1962B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13837,7 +13837,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000002D-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13847,7 +13847,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000002E-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13857,7 +13857,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000002F-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13867,7 +13867,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000030-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13877,7 +13877,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000031-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13887,7 +13887,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000032-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13897,7 +13897,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000033-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13907,7 +13907,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000034-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13917,7 +13917,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000035-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13927,7 +13927,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000036-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13955,7 +13955,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{1F5491FE-DF69-47DA-A288-1A7FD4509AA9}</c15:txfldGUID>
+                      <c15:txfldGUID>{6368E6E5-1D32-4567-B585-EEACDC626AFF}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13968,7 +13968,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000037-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13996,7 +13996,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AAAFCD0C-8690-4691-A222-B90EDA55E29E}</c15:txfldGUID>
+                      <c15:txfldGUID>{0F191038-978B-44D6-A3BD-AEFAECE038A0}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14009,7 +14009,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000038-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14037,7 +14037,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{47ED704B-D5B0-4C4A-B3A0-D05272A067DD}</c15:txfldGUID>
+                      <c15:txfldGUID>{D996D235-21EB-4FE7-BE39-7BC364155B33}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14050,7 +14050,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{00000039-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14078,7 +14078,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{600C7CF7-4FDD-4FA0-8ADE-6774AEF3B5F3}</c15:txfldGUID>
+                      <c15:txfldGUID>{EC3158C5-B782-49F6-97A9-1E572276D103}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14091,7 +14091,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000003A-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14101,7 +14101,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000003B-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14111,7 +14111,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000003C-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14121,7 +14121,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-F2C9-46E7-8EA1-430489EBE003}"/>
+                  <c16:uniqueId val="{0000003D-3383-41D1-9977-0A357D1962B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14284,7 +14284,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000002C-F2C9-46E7-8EA1-430489EBE003}"/>
+              <c16:uniqueId val="{0000002C-3383-41D1-9977-0A357D1962B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14431,7 +14431,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000003E-F2C9-46E7-8EA1-430489EBE003}"/>
+              <c16:uniqueId val="{0000003E-3383-41D1-9977-0A357D1962B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14445,11 +14445,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="1103585936"/>
-        <c:axId val="1018390544"/>
+        <c:axId val="1709137648"/>
+        <c:axId val="1604163856"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1103585936"/>
+        <c:axId val="1709137648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14495,7 +14495,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018390544"/>
+        <c:crossAx val="1604163856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14503,11 +14503,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018390544"/>
+        <c:axId val="1604163856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="200"/>
-          <c:min val="140"/>
+          <c:max val="1.1494252873563218"/>
+          <c:min val="0.8045977011494253"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -14537,7 +14537,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1103585936"/>
+        <c:crossAx val="1709137648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14672,7 +14672,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000008-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14682,7 +14682,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000009-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14710,7 +14710,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EB1A66AB-5896-47D0-9296-C63A58BC75FF}</c15:txfldGUID>
+                      <c15:txfldGUID>{B4BB77E0-2E69-4641-B347-6869AA62A23E}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14723,7 +14723,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14751,7 +14751,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{859771A2-763D-407E-9A7A-55867E86C30D}</c15:txfldGUID>
+                      <c15:txfldGUID>{34254CEC-30D1-45B0-9304-DAAB62BA4115}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14764,7 +14764,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14792,7 +14792,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E2FA52E0-4566-4173-AA51-2BFE1F24B0BC}</c15:txfldGUID>
+                      <c15:txfldGUID>{A5133E19-9983-48D5-B149-393A9A1F3C47}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14805,7 +14805,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000C-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14833,7 +14833,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CCBB5DE8-8EA4-456A-A0C4-000D8A1B79E2}</c15:txfldGUID>
+                      <c15:txfldGUID>{2419F14A-8E2A-4EDD-A400-FCDD2D783F4F}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14846,7 +14846,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000D-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14874,7 +14874,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E9374C4A-76D4-4BE4-A52B-971AE28DC8D2}</c15:txfldGUID>
+                      <c15:txfldGUID>{C93515AA-C620-4DB0-B735-97B278453CCF}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14887,7 +14887,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000E-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14915,7 +14915,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F5F3027E-1C03-4E6A-BBF7-000502DD9218}</c15:txfldGUID>
+                      <c15:txfldGUID>{C5C9C12D-B12A-4613-A7EF-B45B00041185}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14928,7 +14928,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000000F-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14956,7 +14956,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5E640A35-4EFF-4775-8EAF-2A634BD8A4AB}</c15:txfldGUID>
+                      <c15:txfldGUID>{416E0DAD-B4E1-4CC2-8C25-4CA02A737335}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14969,7 +14969,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000010-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14997,7 +14997,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0AAC6A4F-2A54-4D8D-84CF-EC200EDF28B8}</c15:txfldGUID>
+                      <c15:txfldGUID>{09BA1C71-2B50-456B-9CB7-74A4CB4F3C0A}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15010,7 +15010,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000011-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15038,7 +15038,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4051FDEC-0199-4525-87FB-BF4E52CE03BF}</c15:txfldGUID>
+                      <c15:txfldGUID>{0A7E9112-F1C4-4DBA-AD51-C6CBF3F8E90D}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15051,7 +15051,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000012-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15079,7 +15079,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DA21754A-17B0-447A-A09A-CDDB5792ABA0}</c15:txfldGUID>
+                      <c15:txfldGUID>{8D0914F6-389A-4430-BC58-70F831B9CB2E}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15092,7 +15092,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000013-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15120,7 +15120,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0836EE3D-4A92-429B-80E2-2D397D13DA93}</c15:txfldGUID>
+                      <c15:txfldGUID>{B4AEDD58-C361-4207-9953-0DD68C8634F3}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15133,7 +15133,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000014-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15161,7 +15161,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{09218D3B-F436-4171-AA5C-D4149164299B}</c15:txfldGUID>
+                      <c15:txfldGUID>{73354E20-4737-464F-8724-C924656C2691}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15174,7 +15174,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000015-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15202,7 +15202,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0D042913-36E1-4DBC-A106-A1A62AEF4267}</c15:txfldGUID>
+                      <c15:txfldGUID>{F8B24A4D-EFE9-4889-AA02-93FB7C9D91EB}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15215,7 +15215,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000016-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15243,7 +15243,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C734E644-6F48-4887-A526-A4BFC02D10A2}</c15:txfldGUID>
+                      <c15:txfldGUID>{50A540AA-25BA-4119-94C6-5D631F827D47}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15256,7 +15256,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000017-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15284,7 +15284,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FCF1BF4E-6983-4BDE-BF4A-F66844A5EDA8}</c15:txfldGUID>
+                      <c15:txfldGUID>{D09FC147-1FD3-4874-9FA6-5464A01E6654}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15297,7 +15297,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000018-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15307,7 +15307,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000019-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15317,7 +15317,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000001A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15327,7 +15327,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000001B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15508,7 +15508,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-4662-4EBB-8CB3-679626268D32}"/>
+              <c16:uniqueId val="{00000007-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15674,7 +15674,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001C-4662-4EBB-8CB3-679626268D32}"/>
+              <c16:uniqueId val="{0000001C-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15720,7 +15720,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{42E79CC9-FCBC-496D-84E7-4D20C38B20C9}</c15:txfldGUID>
+                      <c15:txfldGUID>{23CEC3B8-9E06-434F-8185-006DBD93ECE7}</c15:txfldGUID>
                       <c15:f>'C06F'!$Z$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15733,7 +15733,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000001E-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15743,7 +15743,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000001F-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15753,7 +15753,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000020-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15763,7 +15763,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000021-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15773,7 +15773,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000022-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15783,7 +15783,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000023-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15793,7 +15793,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000024-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15803,7 +15803,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000025-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15813,7 +15813,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000026-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15823,7 +15823,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000027-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15833,7 +15833,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000028-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15843,7 +15843,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000029-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15853,7 +15853,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15863,7 +15863,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15873,7 +15873,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002C-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15883,7 +15883,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002D-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15893,7 +15893,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002E-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15903,7 +15903,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000002F-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15913,7 +15913,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000030-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15923,7 +15923,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000031-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16104,7 +16104,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-4662-4EBB-8CB3-679626268D32}"/>
+              <c16:uniqueId val="{0000001D-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16138,7 +16138,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000033-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16166,7 +16166,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2790E124-0C50-4F73-848B-FAA035B68393}</c15:txfldGUID>
+                      <c15:txfldGUID>{FC9C01E6-5763-4230-A096-490AB2D1C002}</c15:txfldGUID>
                       <c15:f>'C06F'!$AB$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16179,7 +16179,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000034-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16189,7 +16189,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000035-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16199,7 +16199,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000036-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16209,7 +16209,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000037-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16219,7 +16219,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000038-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16229,7 +16229,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000039-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16239,7 +16239,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16249,7 +16249,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16259,7 +16259,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003C-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16269,7 +16269,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003D-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16279,7 +16279,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003E-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16289,7 +16289,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000003F-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16299,7 +16299,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000040-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000040-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16309,7 +16309,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000041-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16319,7 +16319,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000042-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16329,7 +16329,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000043-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16339,7 +16339,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000044-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16349,7 +16349,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000045-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16359,7 +16359,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000046-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16540,7 +16540,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000032-4662-4EBB-8CB3-679626268D32}"/>
+              <c16:uniqueId val="{00000032-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16574,7 +16574,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000048-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16584,7 +16584,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000049-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16594,7 +16594,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16604,7 +16604,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16614,7 +16614,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004C-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16624,7 +16624,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004D-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16634,7 +16634,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004E-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16644,7 +16644,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004F-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000004F-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16654,7 +16654,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000050-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000050-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16664,7 +16664,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000051-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000051-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16674,7 +16674,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000052-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000052-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16684,7 +16684,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000053-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000053-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16694,7 +16694,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000054-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000054-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16704,7 +16704,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000055-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000055-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16714,7 +16714,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000056-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000056-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16724,7 +16724,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000057-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000057-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16734,7 +16734,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000058-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000058-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16762,7 +16762,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5CB36D7B-7863-4F48-B317-A8DA272A4C13}</c15:txfldGUID>
+                      <c15:txfldGUID>{CCE1A73D-C1C3-48FE-A47B-4739216EAA00}</c15:txfldGUID>
                       <c15:f>'C06F'!$AD$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16775,7 +16775,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000059-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{00000059-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16785,7 +16785,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005A-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000005A-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16795,7 +16795,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005B-4662-4EBB-8CB3-679626268D32}"/>
+                  <c16:uniqueId val="{0000005B-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16976,7 +16976,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000047-4662-4EBB-8CB3-679626268D32}"/>
+              <c16:uniqueId val="{00000047-BEF2-4A4D-BB5B-5B2AC061E26A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16990,11 +16990,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="1103609600"/>
-        <c:axId val="1018493744"/>
+        <c:axId val="1709136256"/>
+        <c:axId val="1604300656"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1103609600"/>
+        <c:axId val="1709136256"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -17018,7 +17018,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018493744"/>
+        <c:crossAx val="1604300656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17026,10 +17026,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018493744"/>
+        <c:axId val="1604300656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2200"/>
+          <c:max val="1.0254537518168634"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -17060,7 +17060,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1103609600"/>
+        <c:crossAx val="1709136256"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17332,7 +17332,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-751A-4E2F-A49E-7FBCF874EDC9}"/>
+              <c16:uniqueId val="{00000007-4F19-4904-89EA-FCDB7DE84761}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -17366,7 +17366,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000009-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17376,7 +17376,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000A-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17404,7 +17404,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ACCA0E80-3310-4DC6-B5C7-F0305B294FB5}</c15:txfldGUID>
+                      <c15:txfldGUID>{49C70779-3D7C-4605-9A21-BE28282BA9D0}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17417,7 +17417,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000B-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17445,7 +17445,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{080C5928-E80B-4C3F-B72D-BDA55854C4AA}</c15:txfldGUID>
+                      <c15:txfldGUID>{B95ED3C3-535E-49F0-8EC6-39FEDD6EF398}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17458,7 +17458,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000C-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17486,7 +17486,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8935CFD7-2CEF-4F16-B9A3-8B8AEEBD4552}</c15:txfldGUID>
+                      <c15:txfldGUID>{3079A9E5-C551-4F8D-B6EC-B69761DBD029}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17499,7 +17499,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000D-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17527,7 +17527,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B3BFA200-A444-4FFE-90F5-02C6AD6A87C9}</c15:txfldGUID>
+                      <c15:txfldGUID>{DF08DCAB-4220-4B36-9426-8AFEF34F4030}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17540,7 +17540,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000E-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17550,7 +17550,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000000F-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17560,7 +17560,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000010-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17570,7 +17570,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000011-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17580,7 +17580,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000012-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17590,7 +17590,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000013-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17600,7 +17600,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000014-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17610,7 +17610,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000015-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17620,7 +17620,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000016-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17630,7 +17630,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000017-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17640,7 +17640,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000018-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17668,7 +17668,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{823B9306-916C-478F-997C-513B1CBC55CE}</c15:txfldGUID>
+                      <c15:txfldGUID>{89B666A4-DB9E-4747-8BC0-3FAF3A3E6968}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17681,7 +17681,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000019-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17691,7 +17691,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000001A-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17701,7 +17701,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000001B-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17729,7 +17729,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{63C04EB4-5928-45E8-83FE-6226C4A6A8F2}</c15:txfldGUID>
+                      <c15:txfldGUID>{837B0154-5933-4BD1-9001-75A359B1AAC4}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$30</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17742,7 +17742,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000001C-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17923,7 +17923,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-751A-4E2F-A49E-7FBCF874EDC9}"/>
+              <c16:uniqueId val="{00000008-4F19-4904-89EA-FCDB7DE84761}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -17957,7 +17957,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000001E-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17967,7 +17967,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000001F-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17977,7 +17977,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000020-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17987,7 +17987,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000021-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17997,7 +17997,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000022-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18007,7 +18007,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000023-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18035,7 +18035,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F94F6D69-98F8-4F78-9378-15C730E55EAB}</c15:txfldGUID>
+                      <c15:txfldGUID>{186592A1-9AB9-49BB-A245-F0839E50F2CF}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18048,7 +18048,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000024-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18076,7 +18076,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C9EDC2E0-8BE0-4F9B-83A2-B8A538A6F0BC}</c15:txfldGUID>
+                      <c15:txfldGUID>{42CC2AB1-286A-462B-AE5C-B18A9E942E8E}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18089,7 +18089,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000025-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18117,7 +18117,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6C34BD33-3752-4E2A-9F8C-066058854BFD}</c15:txfldGUID>
+                      <c15:txfldGUID>{A8997030-5ED1-4DCF-801E-1E35CBA3F71F}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18130,7 +18130,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000026-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18158,7 +18158,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{976A741A-33FE-4734-A6E2-E00CD7F9B017}</c15:txfldGUID>
+                      <c15:txfldGUID>{47EBB291-B2CE-49CF-BAFB-1512598B4FDC}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18171,7 +18171,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000027-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18199,7 +18199,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A758E03F-EBCC-4B12-A502-33CEA820AAA5}</c15:txfldGUID>
+                      <c15:txfldGUID>{31B07BB5-4F39-4BDC-8429-07DD4B7B060A}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18212,7 +18212,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000028-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18240,7 +18240,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E0F2EA31-3D4E-48B6-87EF-36F1CB7F65DA}</c15:txfldGUID>
+                      <c15:txfldGUID>{E8E00964-34DD-4655-887B-FD748F86B457}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18253,7 +18253,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000029-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18281,7 +18281,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BC9E7B3B-7F60-4690-86E5-E4BCB3E8D2BE}</c15:txfldGUID>
+                      <c15:txfldGUID>{D69987FE-36DD-4C5D-B703-B926EEE18C05}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18294,7 +18294,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002A-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18322,7 +18322,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6F5EF9A8-2EE2-40A9-BA67-2F9A754FA1EB}</c15:txfldGUID>
+                      <c15:txfldGUID>{61687A26-CB8A-4CC3-BE1F-1075ACD6B21C}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18335,7 +18335,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002B-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18363,7 +18363,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{13D14704-F77C-40A8-AA41-7CADE6DCB077}</c15:txfldGUID>
+                      <c15:txfldGUID>{A9CF4921-176F-42A5-B448-D85F3778A5BC}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18376,7 +18376,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002C-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18404,7 +18404,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{74957A68-7BF6-4C40-994D-5B99D4C21F84}</c15:txfldGUID>
+                      <c15:txfldGUID>{9ED19070-8496-46A7-AC4A-369E0FAEAFFD}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18417,7 +18417,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002D-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18427,7 +18427,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002E-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18437,7 +18437,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{0000002F-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18465,7 +18465,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D3F107E8-560D-4895-B836-0CACD7B97491}</c15:txfldGUID>
+                      <c15:txfldGUID>{9AACEA4C-F19F-436C-983F-28E97D0DE6C2}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18478,7 +18478,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000030-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18488,7 +18488,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-751A-4E2F-A49E-7FBCF874EDC9}"/>
+                  <c16:uniqueId val="{00000031-4F19-4904-89EA-FCDB7DE84761}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18669,7 +18669,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-751A-4E2F-A49E-7FBCF874EDC9}"/>
+              <c16:uniqueId val="{0000001D-4F19-4904-89EA-FCDB7DE84761}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18683,11 +18683,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="70894208"/>
-        <c:axId val="1018361744"/>
+        <c:axId val="677978832"/>
+        <c:axId val="1604157136"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70894208"/>
+        <c:axId val="677978832"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -18704,7 +18704,7 @@
             </a:solidFill>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="1018361744"/>
+        <c:crossAx val="1604157136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -18712,11 +18712,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018361744"/>
+        <c:axId val="1604157136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2200"/>
-          <c:min val="1600"/>
+          <c:max val="1.0254537518168634"/>
+          <c:min val="0.74578454677590056"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -18746,7 +18746,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="70894208"/>
+        <c:crossAx val="677978832"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19018,7 +19018,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-970C-44B9-9296-8C08EE8A6E43}"/>
+              <c16:uniqueId val="{00000007-320D-4ECD-A575-88FC49D4D6DC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19070,7 +19070,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{45A19334-2140-46C8-8BC9-62B928208363}</c15:txfldGUID>
+                      <c15:txfldGUID>{4CD29057-FB05-47A4-96E6-91006E301955}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19083,7 +19083,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000011-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19111,7 +19111,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{14302B2A-C826-4F21-BD92-0287B943CC6B}</c15:txfldGUID>
+                      <c15:txfldGUID>{17A5598E-EDF1-4536-AAF7-B5E5F72DDF0E}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19124,7 +19124,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000012-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19152,7 +19152,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6B12E19E-78F7-4CD7-97CA-2BA68364F875}</c15:txfldGUID>
+                      <c15:txfldGUID>{EFED419D-7D9E-44F8-BC0D-AF2EFC2139F9}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19165,7 +19165,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000013-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19193,7 +19193,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AAF5BB9E-F03F-41E5-A469-62F70B42DA21}</c15:txfldGUID>
+                      <c15:txfldGUID>{0ECD9882-6693-4F5B-8FB1-584319F94C53}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19206,7 +19206,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000014-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19234,7 +19234,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3C8027B1-A45A-4E89-A406-E7592DC8C2B7}</c15:txfldGUID>
+                      <c15:txfldGUID>{E23902DA-3FB6-4715-87D3-3127FDDC80C6}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19247,7 +19247,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000015-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19275,7 +19275,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2CCF61FD-F52E-4353-91A4-1A9FB88DA0BA}</c15:txfldGUID>
+                      <c15:txfldGUID>{BA1F9B91-17F9-46F9-ACC8-FCE4671259A0}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19288,7 +19288,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000016-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19298,7 +19298,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000009-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19308,7 +19308,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000A-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19318,7 +19318,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000B-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19328,7 +19328,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000C-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19338,7 +19338,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000D-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19348,7 +19348,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000E-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19376,7 +19376,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0CE5AAEC-E281-4186-9745-D51B419B8D2E}</c15:txfldGUID>
+                      <c15:txfldGUID>{BF1404B2-C54A-4112-A5B6-88B1545F109E}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19389,7 +19389,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000017-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19417,7 +19417,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4D820104-B192-4254-A683-86E8DCEC8859}</c15:txfldGUID>
+                      <c15:txfldGUID>{35DC31A9-F428-4BBE-80CF-10745DF02A64}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19430,7 +19430,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000018-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19458,7 +19458,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{913CBDA8-C60C-439C-816C-E3D4F8ABD1E3}</c15:txfldGUID>
+                      <c15:txfldGUID>{BA1D2EA6-8C9A-47BC-ADB6-E62514F549F8}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19471,7 +19471,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000019-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19499,7 +19499,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B5EC13A4-EBA1-41E4-B6ED-0E8ED40AA8A2}</c15:txfldGUID>
+                      <c15:txfldGUID>{82F5290A-99C4-4C6B-8502-795D1224D6E6}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19512,7 +19512,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000001A-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19522,7 +19522,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000000F-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19550,7 +19550,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{12DB6C89-2C71-4BC8-8E00-122E279A6817}</c15:txfldGUID>
+                      <c15:txfldGUID>{E38CDA60-099E-4752-A2D9-D50C92059F68}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19563,7 +19563,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000001B-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19573,7 +19573,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000010-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19601,7 +19601,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{661DBC4B-1944-481F-8121-B7605CEBFC64}</c15:txfldGUID>
+                      <c15:txfldGUID>{1E6DD72C-D89E-49ED-9BC6-BB726E8B18FA}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$30</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19614,7 +19614,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000001C-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19798,7 +19798,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-970C-44B9-9296-8C08EE8A6E43}"/>
+              <c16:uniqueId val="{00000008-320D-4ECD-A575-88FC49D4D6DC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19832,7 +19832,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000001E-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19842,7 +19842,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000001F-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19852,7 +19852,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000020-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19862,7 +19862,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000021-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19872,7 +19872,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000022-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19882,7 +19882,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000023-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19910,7 +19910,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8EC20D52-279E-4D7E-AD77-C1AC2C49EDFE}</c15:txfldGUID>
+                      <c15:txfldGUID>{5D2494DF-EBEB-4DA0-8071-C55ADC11EEE6}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19923,7 +19923,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002A-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19951,7 +19951,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D223E401-09B0-4D39-8640-0E0B948549F6}</c15:txfldGUID>
+                      <c15:txfldGUID>{E4A0D909-1B46-491C-B298-9FC2D132264C}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19964,7 +19964,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002B-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19992,7 +19992,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AB848803-5F8C-4F20-BA46-E2608382C4B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{D7079D4B-CD97-477B-A851-C8CFB4F9A51D}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20005,7 +20005,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002C-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20033,7 +20033,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3F81076C-804A-4867-81C6-B251E163EE07}</c15:txfldGUID>
+                      <c15:txfldGUID>{8E2C5222-23D2-4018-B3BE-CB94863F7252}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20046,7 +20046,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002D-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20074,7 +20074,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A8049C65-D799-4364-9FE3-7920238F8CBC}</c15:txfldGUID>
+                      <c15:txfldGUID>{159D9B0F-D6C3-4A5C-9BD2-6028FF006484}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20087,7 +20087,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002E-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20115,7 +20115,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{66598B29-DD66-49DA-992F-5D51C4BC282A}</c15:txfldGUID>
+                      <c15:txfldGUID>{46C4CC34-9655-40BE-8627-A18D4F6763A7}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20128,7 +20128,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{0000002F-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20138,7 +20138,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000024-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20148,7 +20148,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000025-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20158,7 +20158,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000026-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20168,7 +20168,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000027-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20196,7 +20196,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9DE64BB7-D479-43E0-B529-BFBF32DE786F}</c15:txfldGUID>
+                      <c15:txfldGUID>{1D695A53-7FD7-4C56-A144-EED3CAD75798}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20209,7 +20209,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000030-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20219,7 +20219,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000028-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20247,7 +20247,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9EC8FB18-D342-46F6-8F05-0BF7D329485E}</c15:txfldGUID>
+                      <c15:txfldGUID>{407BFA8D-BC58-45A4-A8FE-EB47F2CEE510}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20260,7 +20260,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000031-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20270,7 +20270,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-970C-44B9-9296-8C08EE8A6E43}"/>
+                  <c16:uniqueId val="{00000029-320D-4ECD-A575-88FC49D4D6DC}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20454,7 +20454,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-970C-44B9-9296-8C08EE8A6E43}"/>
+              <c16:uniqueId val="{0000001D-320D-4ECD-A575-88FC49D4D6DC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -20468,11 +20468,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="70844560"/>
-        <c:axId val="1018505264"/>
+        <c:axId val="677931968"/>
+        <c:axId val="1604275216"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70844560"/>
+        <c:axId val="677931968"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -20496,7 +20496,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1018505264"/>
+        <c:crossAx val="1604275216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20504,10 +20504,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1018505264"/>
+        <c:axId val="1604275216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1120"/>
+          <c:max val="1.055607917059378"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -20538,7 +20538,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="70844560"/>
+        <c:crossAx val="677931968"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20632,7 +20632,7 @@
         <xdr:cNvPr id="2" name="panel_area">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98620D20-F54E-79D4-A515-BFB712B2A1C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FB0EE2C-BBB0-4957-2B77-EA55103091E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20668,7 +20668,7 @@
         <xdr:cNvPr id="3" name="title_C01A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72DDBFB3-B484-67D3-CDDA-449CBD22C0F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52209257-9E19-EDBF-224C-2816702DFE6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20725,7 +20725,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{7C9BEBAB-B5DD-49E1-8EFA-597483740B5A}" type="TxLink">
+          <a:fld id="{793B7635-9D64-4F53-86C8-DBF42B993E9E}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -20761,7 +20761,7 @@
         <xdr:cNvPr id="4" name="title_C01A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{823E6EFB-812F-7E56-1658-78D5D07529B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E66096A5-7C11-336A-8930-57FC97213FE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20818,7 +20818,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{436C7A4F-3A8C-407D-A76F-279B1B037AC1}" type="TxLink">
+          <a:fld id="{F9767F36-3972-4B72-801E-9DA5ACFE2E06}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -20854,7 +20854,7 @@
         <xdr:cNvPr id="5" name="title_C01A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADD62AEB-D61B-3DBA-A8ED-FFD53EF5F4B8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79591EAE-1E33-F50F-307E-2542ADCF5CE2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20911,7 +20911,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{B1AA984C-EA39-4F14-84A8-E41B0BA0F4CC}" type="TxLink">
+          <a:fld id="{7DABDD56-0D51-46A6-B5E6-A09F31B12AAE}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -20947,7 +20947,7 @@
         <xdr:cNvPr id="6" name="title_C01A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{259E111A-75D2-862C-9848-CD19DC25178D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF6F4F94-D2D6-F885-4385-11971455E9A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21004,7 +21004,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{05EE6B13-629A-45DA-B666-C54F99AE2A07}" type="TxLink">
+          <a:fld id="{80F9D5EA-0347-4BD9-B2D6-645AA698B8E8}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21045,7 +21045,7 @@
         <xdr:cNvPr id="2" name="panel_channel">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CD0975C-E49A-516E-F7CA-19FB2D1B529F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D87FECA0-6AEE-50C0-C21B-4770730BA541}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21081,7 +21081,7 @@
         <xdr:cNvPr id="3" name="title_C02A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{887230CF-7CD0-29AE-FA9F-BF99A27647D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CF956FE-EDC5-72EE-F3F4-F810BD932A1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21138,7 +21138,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{84BF5948-C353-4918-90E4-190BF79CD628}" type="TxLink">
+          <a:fld id="{EBD34086-7108-4A34-AE84-9104AC810061}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21174,7 +21174,7 @@
         <xdr:cNvPr id="4" name="title_C02A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B103E77E-F281-CA51-31C4-1DE6D0556EBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D686F2A6-A37D-5088-4B50-D5BF2D18E522}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21231,7 +21231,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{4B1E4677-AF52-4C32-A30F-D40237418FFF}" type="TxLink">
+          <a:fld id="{B5AC36DC-0875-4CFA-8FC3-497DEA38BC17}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -21267,7 +21267,7 @@
         <xdr:cNvPr id="5" name="title_C02A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A7DA927-158C-D7EB-E5DC-57527E8C4C32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0960196B-5B46-4D14-B236-49F5F01E743B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21324,7 +21324,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{56459075-F1B9-46FB-AB3E-DC6A2E158202}" type="TxLink">
+          <a:fld id="{1D0C5C9C-12F1-432E-A1C7-5463D01B9F8E}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21360,7 +21360,7 @@
         <xdr:cNvPr id="6" name="title_C02A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7659F82-C540-046B-6202-3553F475A9E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86988BF5-3FF7-F0C9-6EBA-129AB451AA48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21417,7 +21417,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{E973387E-8206-4E68-9195-719D0720655A}" type="TxLink">
+          <a:fld id="{992F39B7-4F7C-45FF-83E2-A2EE186A777C}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21458,7 +21458,7 @@
         <xdr:cNvPr id="2" name="title_C03A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7FD30A8-ED15-FD32-2AB6-D787542FF0D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD7696DE-C6F6-EF6B-20D1-61851A20C0F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21515,7 +21515,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{F02687D9-9357-48C7-B52B-DFB6132B18B0}" type="TxLink">
+          <a:fld id="{E71C9D00-BE38-40E9-8975-C4817E01963D}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21551,7 +21551,7 @@
         <xdr:cNvPr id="3" name="title_C03A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DCAB68E-1FD3-A609-4068-312D7F09E9AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{184EE4A3-7F8D-29A5-4E0A-C591ABE84738}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21608,7 +21608,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{5DFF1882-F0DA-47D6-9BAF-5484867CE547}" type="TxLink">
+          <a:fld id="{FE0DF008-6538-4837-9A78-29542805691A}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21644,7 +21644,7 @@
         <xdr:cNvPr id="4" name="title_C03A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE67FF8B-C94E-C239-BA66-BA4447588549}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C6F6DA7-B63A-61CE-D6AE-A5CD760F205C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21701,7 +21701,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{B4D0683F-5B17-4F17-81F0-5655E3D9DE78}" type="TxLink">
+          <a:fld id="{A96C7FE6-8BF2-413C-9A04-BBF25E32FB1C}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21737,7 +21737,7 @@
         <xdr:cNvPr id="5" name="title_C03A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD8B0122-9A37-67C5-8BEC-79C34F2CBCCE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00EE0E13-A9D2-F847-C379-DF347671D172}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21794,7 +21794,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{8DC6E6AA-B5B8-4350-9D3D-D697BFCE7587}" type="TxLink">
+          <a:fld id="{F949985F-C26B-493A-B575-557D648F504A}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21830,7 +21830,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B12AFB-6DF8-7607-23DB-AC6D36077221}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05AEB34B-5CB3-8FE6-69C2-51A06FC5D786}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21871,7 +21871,7 @@
         <xdr:cNvPr id="2" name="title_C04A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E3E4FD-19A5-8A25-9FAE-08B17327B31C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A455A0D1-83EE-9A10-1EA7-BC32EF7FF16A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21928,7 +21928,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{3B99AB19-62E4-4CE6-B029-C5D7D978C5A0}" type="TxLink">
+          <a:fld id="{D9FE9859-8AA9-487B-A273-CD075C9EE6C0}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -21964,7 +21964,7 @@
         <xdr:cNvPr id="3" name="title_C04A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E2905B0-88F6-04C8-7777-7C7C8FBFCD25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9C11330-0FC3-554A-C5BE-D2B2D114DDA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22021,7 +22021,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{E558C898-0DB3-4E47-8DC8-2A79B39B470E}" type="TxLink">
+          <a:fld id="{43C065C7-B71A-4B7D-858D-1FAA6026BC37}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22057,7 +22057,7 @@
         <xdr:cNvPr id="4" name="title_C04A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6050EF7-B4A6-3146-6C9B-A2F42C8E5BD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9BE2FD1-B3B8-2894-3307-C660859916B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22114,7 +22114,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{BD93DADA-C5E7-4D75-A918-12EF522A4EE7}" type="TxLink">
+          <a:fld id="{F3CBD2A5-5783-4AFA-809E-9C8B41071A66}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22150,7 +22150,7 @@
         <xdr:cNvPr id="5" name="title_C04A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B097F127-CF5D-B015-E80C-E4A09CB54501}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDDE8929-52A2-C9ED-9563-21605AF53002}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22207,7 +22207,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{FE97829C-2893-4297-B6A9-8CB6228F698B}" type="TxLink">
+          <a:fld id="{93DC05CB-240B-41A9-A991-4CE7188F6736}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22243,7 +22243,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA53C611-D300-676E-5AF2-5EFED79919D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A451D297-C3AB-40AE-399E-9A9C8210C2F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22284,7 +22284,7 @@
         <xdr:cNvPr id="2" name="title_C05X_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C20AC05-3166-F7E1-99DB-B11BB5CC65B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DDC202-957C-07AB-8317-5AF84C21E661}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22341,7 +22341,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{58C7CC93-A9EB-4929-A33A-0789BABB4066}" type="TxLink">
+          <a:fld id="{EA20B4E6-8B08-43C2-9FB0-D1866663397E}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22377,7 +22377,7 @@
         <xdr:cNvPr id="3" name="title_C05X_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A899D0CC-0567-EAE4-E6B0-C5C3FCCBF7C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F447E65-123B-9A8E-3E00-D8220FC728A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22434,7 +22434,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{EF96749E-BFBB-4A44-BFF3-20F304882C39}" type="TxLink">
+          <a:fld id="{85871E78-307D-48AF-8E6C-6117B2D193F4}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22470,7 +22470,7 @@
         <xdr:cNvPr id="4" name="title_C05X_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B5BC592-9320-A143-4C13-22A6F4717AAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E36EF6EB-65A9-414F-07DA-3153FCD5E3A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22527,7 +22527,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{9C25A3E2-EC46-4579-88B0-FF05278BB0C2}" type="TxLink">
+          <a:fld id="{DDE7F9C4-6B0C-4CBD-BE02-7B70E14299B3}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22563,7 +22563,7 @@
         <xdr:cNvPr id="5" name="title_C05X_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E147A26-42BA-CC71-10EA-AB92F0C5B1E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C688C1C-DC6F-ABF2-06D7-31B8C799868C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22620,7 +22620,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{D404B77D-F2FE-47DB-915B-37D34B22232E}" type="TxLink">
+          <a:fld id="{80706779-C20B-4443-9175-5628568C6EDA}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22656,7 +22656,7 @@
         <xdr:cNvPr id="6" name="tier_wf">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29EE4D63-88D1-F235-4510-E78F27BEF643}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8D530DF-604A-819F-DE59-F15185A597DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22692,7 +22692,7 @@
         <xdr:cNvPr id="7" name="rule_wf_0">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FBD9576-28D3-54A6-5EF7-C93EA202BD7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{478AA9B1-75C4-45D0-928E-6DB6DA70C219}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22747,7 +22747,7 @@
         <xdr:cNvPr id="8" name="rule_wf_1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABCBAFE7-72B2-781A-9451-B05A1B5715F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{072C3727-3915-E506-3A5E-5BFDA16C2C8F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22807,7 +22807,7 @@
         <xdr:cNvPr id="2" name="title_C06F_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D21E372-2569-5E42-7CE4-2FBE3CC1AD27}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3184EF2E-7819-CB37-17B9-9FF5F891319A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22864,7 +22864,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{5A0B5763-DF59-48B7-9A97-BD1CE8321CF9}" type="TxLink">
+          <a:fld id="{07CC5533-0A02-45C0-9E3E-0BEAE5EA4FA0}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22900,7 +22900,7 @@
         <xdr:cNvPr id="3" name="title_C06F_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79896C9A-1783-86AA-4D41-FDEA29192A38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{748E1FC7-3793-E2B4-4A32-22EA94301A07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22957,7 +22957,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{2E6A5E28-E736-4299-97E2-B0B528EB386C}" type="TxLink">
+          <a:fld id="{4D451A86-E616-4614-A887-0F0B92589D29}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -22993,7 +22993,7 @@
         <xdr:cNvPr id="4" name="title_C06F_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59BB7017-C844-B6B2-CE57-53E28F745C2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC774607-6DD7-6E5C-50CB-64D1B01E6399}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23050,7 +23050,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{2A4633EF-8B04-481C-8FEB-FAAC9436CD60}" type="TxLink">
+          <a:fld id="{72AC21D5-7C48-44ED-AF0D-DA821625D2DF}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23086,7 +23086,7 @@
         <xdr:cNvPr id="5" name="title_C06F_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F4E23A6-F9E3-7C6E-D8AF-4DEF83916DC3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6DA2708-BBCD-CB74-55BA-CC55DF8A3793}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23143,7 +23143,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{4B082023-D1F5-4B38-9052-C3A85301E7F2}" type="TxLink">
+          <a:fld id="{957E914B-E934-43B1-B27D-70BE36487A69}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23179,7 +23179,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE9560F1-4280-E8B0-1652-15D79B6AF395}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F6946DE-DC85-B5C1-320B-8B78A664A7C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23215,7 +23215,7 @@
         <xdr:cNvPr id="7" name="tier_wf">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E3046C-B545-DD50-3F97-011CFEDA8F9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E486CD0-8952-705C-B124-0E954504B937}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23256,7 +23256,7 @@
         <xdr:cNvPr id="2" name="title_C12A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EF7F24-BC75-5D8F-AAA5-A7DB9A1CF4FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D03850C-FE50-F7C9-54D7-78C65240BF95}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23313,7 +23313,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{5CEE00B7-25CA-4EEA-9A7C-1F922652536D}" type="TxLink">
+          <a:fld id="{EE1164AF-2C44-463F-A153-970DA79B9BDF}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23349,7 +23349,7 @@
         <xdr:cNvPr id="3" name="title_C12A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F4C8D1F-F28E-2E4C-A5FC-DA408CDE8E35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F963D8A-091D-5240-0961-C8C98DD8EAFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23406,7 +23406,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{82543028-66F0-4F0D-803C-44ADB0C237B2}" type="TxLink">
+          <a:fld id="{E7C04C84-92E7-43A1-8429-8D53D5B4A4B7}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23442,7 +23442,7 @@
         <xdr:cNvPr id="4" name="title_C12A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705EA08D-ACDD-EA46-C999-3769319D2F0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD0F7681-EE77-0B5B-0AA3-A1B2BA6CA8F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23499,7 +23499,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{A0D0F347-D6BD-4BC3-B537-AA08E56645E9}" type="TxLink">
+          <a:fld id="{EB21A9F3-722D-44B3-967E-1D9660F4E3DC}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23535,7 +23535,7 @@
         <xdr:cNvPr id="5" name="title_C12A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFC92BFE-0EDE-8696-C08E-6BAC30384AB5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBEBB15A-194F-452C-C69B-76419D6948CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23592,7 +23592,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{7E49E352-1981-4F7A-B1B9-B74066985CCB}" type="TxLink">
+          <a:fld id="{D6CF872F-41AB-44E0-AF76-FDA691A4A757}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23628,7 +23628,7 @@
         <xdr:cNvPr id="6" name="tier_wf_ac">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA11D090-0406-6B91-79B8-93B58F6F8807}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C205B58D-4566-D234-D47D-68CE703789A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23965,7 +23965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA159D2D-997E-45C8-B283-23BBB8454C00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD784E5-40EA-4A67-B194-31B22EA58501}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -24067,7 +24067,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C757914-3459-456B-BFE7-F5E8B6D30BFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E33198-9E83-4E57-A396-5E1D6A9476FB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -24515,7 +24515,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B73FACA-9871-4F80-8E0C-148D324ED13B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B07FE8-F90A-43D0-89A4-9ADB7B502767}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -25577,7 +25577,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA1778A-0D7E-446F-8D78-3BDA1BA69A1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77E830F-9F86-4798-9B14-FB52435F8970}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -27251,7 +27251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4C0399-F7C2-49C2-99CB-29E737856A81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2C3A5B-A172-4122-85D4-F411E2EEBAD7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29335,7 +29335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CE72A7-D2EF-49C0-9300-B76CCBC18F8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE8CAD6-DF29-4B4B-8AC9-93F422402AF7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -32928,7 +32928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F62134-99D1-4BC8-A517-853573C14CF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256A2977-EE2F-4661-A48E-19C70751B11E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -36324,7 +36324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A71016-6AC6-429B-8AE4-01BABAE259EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04971039-8796-4CC9-B1D2-0629BE92A947}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/workbooks/IBCS Charts - Simple Variants Only.xlsx
+++ b/workbooks/IBCS Charts - Simple Variants Only.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfphi\AppData\Local\Temp\tmpb3tfqv4x\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfphi\AppData\Local\Temp\tmpk6633o7b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{689E4A8F-F9CE-4984-8DFF-97599189E46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B60F0609-33D2-4247-BA48-2F8A2661E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{280912EF-7CCC-4092-B7E3-6080E3339CC8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D9ED42D5-617B-44AA-B17E-491DE2CBA7D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{B0568BE9-C701-462F-BBC1-4FD3EAE3A1CD}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{1AC72668-EB3E-4F2F-89B8-7E85DA286A61}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{93404ABC-002D-45AD-BAAA-B22AAB694C24}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{6C0892A5-BA98-4054-8226-6B77A1769A97}">
       <text>
         <r>
           <rPr>
@@ -96,7 +96,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{218249D5-A0CC-4D8C-8BEC-326583589FD5}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{11C01A88-DE24-44BA-A076-4885CA836B6B}">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{18AD91D2-D191-42B6-9DCF-FC525B605B42}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{24491F0D-79C8-4E05-A2CB-F8891A55195C}">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{E3703D17-7CF0-44FD-A5E4-9CD4927643C4}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{06AC6C66-E6B2-4DA2-9DA0-47A0E1154AFA}">
       <text>
         <r>
           <rPr>
@@ -148,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{89A7FF02-FD31-4320-A492-19D599050F0D}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{42AFBB91-BA67-4356-8944-DD35B10CF312}">
       <text>
         <r>
           <rPr>
@@ -172,7 +172,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{712F31F7-4168-4150-B8BE-762423E8AA87}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{0CCE6FD6-DCE8-4A14-92CE-863C01B5994A}">
       <text>
         <r>
           <rPr>
@@ -186,7 +186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F4815749-D0D5-413C-A206-90B43BDEC53F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B437E4A2-86DD-4188-8093-D687453A5C11}">
       <text>
         <r>
           <rPr>
@@ -210,7 +210,7 @@
     <author>Wayne Phillips</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{D786E146-3774-4209-8C6B-63B71AF093B8}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{FC1527D3-6717-4CC4-AE1F-007C1D3BD9C7}">
       <text>
         <r>
           <rPr>
@@ -224,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{3A834A6A-6F15-4C8A-99EA-F6A2CA05F4A2}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{3FE907E4-8282-4CE5-8AEE-2E13EB24931E}">
       <text>
         <r>
           <rPr>
@@ -1334,7 +1334,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{982E7A4C-D915-488B-A494-968A3FCE8B54}</c15:txfldGUID>
+                      <c15:txfldGUID>{590E80C4-79A7-426C-B6BC-F65ECA2CE007}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1347,7 +1347,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000005-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1407,7 +1407,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{366F5AAF-2E43-4550-BF63-72BA778533F5}</c15:txfldGUID>
+                      <c15:txfldGUID>{A87EB259-8197-416F-A1C5-AC3FB7A57B93}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1420,7 +1420,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000006-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1480,7 +1480,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{726BBFE0-D6A6-421C-B1EA-C7DE7E53033C}</c15:txfldGUID>
+                      <c15:txfldGUID>{03133578-D463-44A8-B870-E290CCAAE41B}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1493,7 +1493,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000007-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1553,7 +1553,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8879E8E0-4C09-4B4D-B64D-CFA83C4DC01A}</c15:txfldGUID>
+                      <c15:txfldGUID>{2EFEF57B-E7FD-44A3-8B7E-3DB6E6B41F9D}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$48</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1566,7 +1566,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000008-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1654,7 +1654,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{00000004-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1738,7 +1738,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D4462AAB-8AF7-4A9B-9D50-943A69A7B27F}</c15:txfldGUID>
+                      <c15:txfldGUID>{163AE6BB-AF17-4258-B3EC-8A01FE8098D4}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1751,7 +1751,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000000A-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1811,7 +1811,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{55593A5A-DCAE-4B41-8EDA-759923CE39E6}</c15:txfldGUID>
+                      <c15:txfldGUID>{4836A5A3-D1F7-4741-A68B-6A55A1DACBC3}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1824,7 +1824,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000000B-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1884,7 +1884,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{74005671-D749-4618-B2A6-D33CC2D57DA9}</c15:txfldGUID>
+                      <c15:txfldGUID>{A076FFA9-7851-4F05-A0AE-16A8212BF3A9}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1897,7 +1897,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000000C-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1957,7 +1957,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C19ED87D-3E81-432C-BACB-12565D84C50C}</c15:txfldGUID>
+                      <c15:txfldGUID>{87D35118-A9C9-4897-81C0-0F5E1F64CF5F}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$49</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -1970,7 +1970,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000000D-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2058,7 +2058,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{00000009-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2139,7 +2139,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5F86F036-A2D0-485C-AE97-DDE7FA834593}</c15:txfldGUID>
+                      <c15:txfldGUID>{2A98763D-AF73-4A42-83C0-F8ACCE23A9FE}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2149,7 +2149,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000000F-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2206,7 +2206,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9E14505F-CD9A-4702-BDB4-75140BDB2153}</c15:txfldGUID>
+                      <c15:txfldGUID>{6087EFB8-0DC4-42C1-8790-4FA7C68F0E2D}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2216,7 +2216,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000010-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2273,7 +2273,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A62DADF6-FF4D-4D76-88E1-FA10CF762CEC}</c15:txfldGUID>
+                      <c15:txfldGUID>{7E9165C1-584F-48B3-83AF-2C814E4B85DA}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2283,7 +2283,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000011-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2343,7 +2343,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{957E440A-E9E9-4DEB-89F5-5CDD6A08EF16}</c15:txfldGUID>
+                      <c15:txfldGUID>{29EFD24B-0A37-4A9C-AEA7-959BFE2EF55D}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$50</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2356,7 +2356,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000012-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2444,7 +2444,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{0000000E-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2528,7 +2528,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7D52CCF3-5F39-44F7-A1CE-ED750B10D1C1}</c15:txfldGUID>
+                      <c15:txfldGUID>{DF438134-6221-4EA6-BBA6-197C4B54A5CB}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2541,7 +2541,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000014-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2601,7 +2601,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C75144D1-505F-4A54-A871-E1FA37EB658A}</c15:txfldGUID>
+                      <c15:txfldGUID>{45703C87-1870-46D4-A025-EBAE14F03B7E}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2614,7 +2614,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000015-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2674,7 +2674,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{82D75DA2-32C9-4E85-89EF-5DCBF2F6F5CF}</c15:txfldGUID>
+                      <c15:txfldGUID>{966A7F6A-2F31-4E8E-A3A0-E946B366C756}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2687,7 +2687,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000016-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2747,7 +2747,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{28D9C5F4-F636-4462-A080-735BBF90CCCD}</c15:txfldGUID>
+                      <c15:txfldGUID>{C3B1F4CC-B7DD-4819-A698-489D1CF7D85F}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$51</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2760,7 +2760,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000017-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2848,7 +2848,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000013-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{00000013-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2929,7 +2929,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D83A7A36-F842-4EB7-AAD5-FF100204A413}</c15:txfldGUID>
+                      <c15:txfldGUID>{A118C7B7-17A1-4367-9E7B-D1F11C65F3C7}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -2939,7 +2939,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000019-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2996,7 +2996,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{102755B4-56DF-45A2-9582-B32F44A641B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{6F61226F-100C-4AA3-8830-EA96197A65C4}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3006,7 +3006,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000001A-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3063,7 +3063,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F3601E96-379E-4437-86CE-97768A5000D0}</c15:txfldGUID>
+                      <c15:txfldGUID>{3AAA9DF9-937D-4F9E-B2D4-3B33ED1AEA45}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3073,7 +3073,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000001B-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3130,7 +3130,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D6027822-4491-492A-AAC8-C720937370A6}</c15:txfldGUID>
+                      <c15:txfldGUID>{39B46EBA-B4DC-481B-9CAF-F51CB12E8CA5}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$52</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3140,7 +3140,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000001C-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3228,7 +3228,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000018-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{00000018-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3242,8 +3242,8 @@
         </c:dLbls>
         <c:gapWidth val="44"/>
         <c:overlap val="100"/>
-        <c:axId val="1206626191"/>
-        <c:axId val="1199089935"/>
+        <c:axId val="2053104624"/>
+        <c:axId val="1903527440"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3332,7 +3332,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B9E65972-47B2-4FB2-BACF-404163255F70}</c15:txfldGUID>
+                      <c15:txfldGUID>{292D8DF2-BC58-4265-856D-45C74AAAAA80}</c15:txfldGUID>
                       <c15:f>'C01A'!$B$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3345,7 +3345,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000001E-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3402,7 +3402,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6B3285B0-CF52-4E77-B34F-A1BDCC5AB3B8}</c15:txfldGUID>
+                      <c15:txfldGUID>{586313A7-1264-4849-8FE7-9D678A410E79}</c15:txfldGUID>
                       <c15:f>'C01A'!$C$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3415,7 +3415,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{0000001F-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3472,7 +3472,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4A452DD7-857E-42A4-B9D8-CA3E3296878A}</c15:txfldGUID>
+                      <c15:txfldGUID>{68FFDD28-9DE7-4CA9-9719-5723861BB17A}</c15:txfldGUID>
                       <c15:f>'C01A'!$D$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3485,7 +3485,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000020-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3542,7 +3542,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AC775ADA-877D-4F4C-A5A9-DEC1938CA478}</c15:txfldGUID>
+                      <c15:txfldGUID>{7D1EC86E-FB88-44C0-B5FF-D592F8EEEB24}</c15:txfldGUID>
                       <c15:f>'C01A'!$E$53</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3555,7 +3555,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-E524-499A-8F0D-2387D7025858}"/>
+                  <c16:uniqueId val="{00000021-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3641,7 +3641,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-E524-499A-8F0D-2387D7025858}"/>
+              <c16:uniqueId val="{0000001D-BEB8-477B-AB53-D7B1D6B4E7CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3655,11 +3655,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1206626191"/>
-        <c:axId val="1199089935"/>
+        <c:axId val="2053104624"/>
+        <c:axId val="1903527440"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1206626191"/>
+        <c:axId val="2053104624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3683,7 +3683,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1199089935"/>
+        <c:crossAx val="1903527440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3691,7 +3691,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1199089935"/>
+        <c:axId val="1903527440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.1776251226692835"/>
@@ -3725,7 +3725,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1206626191"/>
+        <c:crossAx val="2053104624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3895,7 +3895,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7942E9AA-909D-4567-8C32-992EDC2BABC9}</c15:txfldGUID>
+                      <c15:txfldGUID>{1D510933-5D7B-4F90-B276-A46BCE44397D}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3908,7 +3908,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000005-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3968,7 +3968,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{628C51F7-F0ED-4C3A-9097-D3C684F31590}</c15:txfldGUID>
+                      <c15:txfldGUID>{319B690E-A8D3-4719-9D21-255DD67D3969}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -3981,7 +3981,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000006-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4041,7 +4041,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DB6FD3FD-FAD4-45F4-8599-036F7E73CFE5}</c15:txfldGUID>
+                      <c15:txfldGUID>{3C32EA7B-E048-43FA-BA07-87F570A9AED2}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4054,7 +4054,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000007-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4114,7 +4114,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2D3D0A89-A502-4181-95A7-589E81B12A2C}</c15:txfldGUID>
+                      <c15:txfldGUID>{D0B71413-620F-42BC-AB6E-DB717EBBF6B0}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4127,7 +4127,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000008-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4187,7 +4187,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5068E22B-3206-4DF2-9EAF-3E5F776BEC63}</c15:txfldGUID>
+                      <c15:txfldGUID>{D81CF573-2472-45F5-9078-32C512F9DE7D}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4200,7 +4200,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000009-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4260,7 +4260,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F840F54F-7915-4EE9-83A9-07C3010BD0F0}</c15:txfldGUID>
+                      <c15:txfldGUID>{520F42B6-899E-4299-B6DA-9C8C3DBD457D}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4273,7 +4273,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000A-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4333,7 +4333,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{29FDE009-BA75-49DE-908D-A255DEBC82CD}</c15:txfldGUID>
+                      <c15:txfldGUID>{804916EB-BD36-4454-A493-37164B9073D1}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4346,7 +4346,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000B-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4406,7 +4406,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0C82C74A-5100-4E23-A8BC-43CBA49A0FE4}</c15:txfldGUID>
+                      <c15:txfldGUID>{CB29670E-BCF9-440B-9FA1-D74A95837EA8}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4419,7 +4419,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000C-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4479,7 +4479,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3D0915E7-0BFE-4024-AD55-2CBF7572FC7B}</c15:txfldGUID>
+                      <c15:txfldGUID>{D1730479-CE53-4228-BACF-43CA17BECBAC}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4492,7 +4492,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000D-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4552,7 +4552,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C2ABD8F3-693F-4B76-A215-6EF7DE8B2D08}</c15:txfldGUID>
+                      <c15:txfldGUID>{F79615C1-5877-4B0F-B3C7-3CEAF2E0EFD4}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4565,7 +4565,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000E-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4625,7 +4625,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7110FB26-0BCE-4F0D-BAD7-467AD102C659}</c15:txfldGUID>
+                      <c15:txfldGUID>{B7FEB35A-D886-4622-A17E-3C10C3A1EC39}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4638,7 +4638,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000000F-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4695,7 +4695,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E3439AAE-2D2E-44D1-B963-133203CA5D0F}</c15:txfldGUID>
+                      <c15:txfldGUID>{7F693015-6523-4400-B13A-8066610CBD33}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4705,7 +4705,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000010-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4762,7 +4762,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A47183B4-9B3D-45FE-922B-4459B4CA13FC}</c15:txfldGUID>
+                      <c15:txfldGUID>{BF5C3DF3-36F6-4BF0-84E6-ADE9C9C86FFC}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4772,7 +4772,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000011-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4832,7 +4832,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4D0E9EDB-86E6-4617-ABF0-507158B7267A}</c15:txfldGUID>
+                      <c15:txfldGUID>{1E57905F-DE53-4B6B-934D-892AC0878CFE}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4845,7 +4845,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000012-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4905,7 +4905,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9D275C58-79BC-46A5-8520-A6FC2DECF4DD}</c15:txfldGUID>
+                      <c15:txfldGUID>{96488EDE-91F9-468A-A9A2-7120B5ACD59B}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4918,7 +4918,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000013-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4978,7 +4978,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F4448668-1DA5-44BC-865B-0F01818B11BA}</c15:txfldGUID>
+                      <c15:txfldGUID>{BEF2BE26-BD1B-4F04-A128-4C94FF1ED7B9}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -4991,7 +4991,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000014-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5051,7 +5051,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{581550E9-EF4C-4136-9A45-5911105BD28F}</c15:txfldGUID>
+                      <c15:txfldGUID>{C5FBAEB4-EFB7-48EC-B7BB-30A8EAADFE4D}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5064,7 +5064,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000015-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5121,7 +5121,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BB43C817-C5D4-41D1-B954-F5DFF61B635B}</c15:txfldGUID>
+                      <c15:txfldGUID>{EFC68BEB-69CF-488B-A3FF-F9E09430E59D}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5131,7 +5131,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000016-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5191,7 +5191,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{49BEE098-1A35-4639-8625-C3D7E11A7B25}</c15:txfldGUID>
+                      <c15:txfldGUID>{04B6CCE7-35B3-4DB6-8425-056440E638C0}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$44</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5204,7 +5204,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000017-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5382,7 +5382,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-3552-487A-9688-B54672F5703D}"/>
+              <c16:uniqueId val="{00000004-18F0-48D4-A89B-63A5BC52AF79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5466,7 +5466,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{19A9FC22-357B-4F19-AF74-8263BADC43A1}</c15:txfldGUID>
+                      <c15:txfldGUID>{C0CFBB29-61CB-4155-923C-F30163D0C5BE}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5479,7 +5479,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000019-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5539,7 +5539,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{35E27B49-6CB1-4A45-857B-DF01FC56C587}</c15:txfldGUID>
+                      <c15:txfldGUID>{598564B7-5CAA-4483-88CD-FB1EFDF48E57}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5552,7 +5552,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001A-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5612,7 +5612,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B6D63DE0-69F4-4A7A-8FBE-174250546964}</c15:txfldGUID>
+                      <c15:txfldGUID>{9DFAB46C-3C97-4DA8-8D79-42C1A462BCE8}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5625,7 +5625,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001B-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5685,7 +5685,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{1CAC0C5E-5470-4B60-9F5A-E80EFD9FF75D}</c15:txfldGUID>
+                      <c15:txfldGUID>{03C1F86A-58F5-4BA3-A03B-CC36FAAA20DC}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5698,7 +5698,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001C-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5758,7 +5758,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C371E5B2-A6BF-4ED5-A416-18268F4BB2F7}</c15:txfldGUID>
+                      <c15:txfldGUID>{42943DE6-3451-4CAB-9660-24DD2AA2F8AE}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5771,7 +5771,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001D-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5831,7 +5831,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{223C874C-F926-4988-A1D6-C79084CD5BD3}</c15:txfldGUID>
+                      <c15:txfldGUID>{67A343CA-9E0C-48F0-87EF-076CB645FA3A}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5844,7 +5844,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001E-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5904,7 +5904,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7DE8510C-BAE1-4B78-9243-8C297457C71A}</c15:txfldGUID>
+                      <c15:txfldGUID>{3740D043-4E6A-4BE0-9928-4DDFA6279B7E}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5917,7 +5917,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000001F-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -5977,7 +5977,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C6314235-8FE9-409C-9431-75863EECBF5E}</c15:txfldGUID>
+                      <c15:txfldGUID>{4C1C8E2D-F558-4F2A-9CD5-9EA2D2EF0617}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -5990,7 +5990,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000020-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6050,7 +6050,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C7F0B32C-C1E5-417D-A412-88BD8043E8CD}</c15:txfldGUID>
+                      <c15:txfldGUID>{63F79313-B43C-4579-8370-003759E2C1AF}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6063,7 +6063,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000021-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6123,7 +6123,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DEF59725-DE03-4A41-BB31-4B36B6BB86C3}</c15:txfldGUID>
+                      <c15:txfldGUID>{D27EAE36-8807-4FF8-A62B-CC304F3FC935}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6136,7 +6136,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000022-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6196,7 +6196,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{75505A27-57B2-454C-B671-BFDD453A30E5}</c15:txfldGUID>
+                      <c15:txfldGUID>{141791CA-97AE-4D4B-92CA-9DCBAE19E394}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6209,7 +6209,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000023-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6269,7 +6269,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{24CD30C5-6828-4DE1-918B-1E3B7550D585}</c15:txfldGUID>
+                      <c15:txfldGUID>{B1A7F52E-C95D-44A2-8FAA-366203EFCD91}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6282,7 +6282,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000024-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6339,7 +6339,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AEDB7B22-D624-4740-BD30-46FB15BA7415}</c15:txfldGUID>
+                      <c15:txfldGUID>{492D71F8-FB83-431E-AED3-6A4E64865F0C}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6349,7 +6349,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000025-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6409,7 +6409,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F3EC962F-7A56-4B9B-8E6C-D921150D562B}</c15:txfldGUID>
+                      <c15:txfldGUID>{B118ED4A-A5DE-41F2-935B-8498912B33A3}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6422,7 +6422,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000026-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6482,7 +6482,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{07B824BA-9F1D-41EE-B27D-422AEF52BC49}</c15:txfldGUID>
+                      <c15:txfldGUID>{9E8038DD-13D0-476C-B8B9-04B3810AD3A2}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6495,7 +6495,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000027-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6555,7 +6555,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3CF66A36-DB5F-47AF-8A69-33CB181E79B5}</c15:txfldGUID>
+                      <c15:txfldGUID>{96FA8B02-4750-470F-902A-1A440103EC4A}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6568,7 +6568,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000028-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6628,7 +6628,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D4D7CE30-7FB5-43AA-B282-97ECBE0FE8CB}</c15:txfldGUID>
+                      <c15:txfldGUID>{13B50B3B-22D1-47C6-87EB-2DBAEB1BB11A}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6641,7 +6641,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000029-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6698,7 +6698,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{99137975-FA35-4FE7-B8F6-F2AA76D6D9AD}</c15:txfldGUID>
+                      <c15:txfldGUID>{264E01D9-E6D4-4019-B950-A4E207DA17CE}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6708,7 +6708,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000002A-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6768,7 +6768,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E6E17D8D-4619-4E75-B517-CBB7A5054FF8}</c15:txfldGUID>
+                      <c15:txfldGUID>{26DAA69F-C1A2-482E-B202-148F1E7C73E1}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$45</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -6781,7 +6781,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000002B-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6959,7 +6959,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000018-3552-487A-9688-B54672F5703D}"/>
+              <c16:uniqueId val="{00000018-18F0-48D4-A89B-63A5BC52AF79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7043,7 +7043,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4C32BFF9-4421-422B-9984-4CFB26DC3570}</c15:txfldGUID>
+                      <c15:txfldGUID>{E224C487-E3A7-4909-A477-5DA2A3F44D1F}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7056,7 +7056,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000002D-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7116,7 +7116,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{59AB9F47-EDCC-4AC3-89C1-AAC3FA65DC4A}</c15:txfldGUID>
+                      <c15:txfldGUID>{2B3763EB-7651-45DC-AA78-B52DE7B5DE50}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7129,7 +7129,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000002E-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7189,7 +7189,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6A72129A-BC0D-4F86-9CCC-5F9E3A4B098E}</c15:txfldGUID>
+                      <c15:txfldGUID>{8183E17D-8729-463A-92CA-66AEF1C8986F}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7202,7 +7202,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000002F-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7262,7 +7262,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{02D5A804-23B9-4050-BE6F-E9B18F4429D0}</c15:txfldGUID>
+                      <c15:txfldGUID>{A9F50B5F-740D-491E-9053-7F0E05A930F1}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7275,7 +7275,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000030-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7335,7 +7335,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{59E00C48-2326-4711-8F0A-776CBDC38440}</c15:txfldGUID>
+                      <c15:txfldGUID>{AAE82400-AAA2-4A6E-B59D-BE051DF410DE}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7348,7 +7348,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000031-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7408,7 +7408,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C7BE3219-5FB3-4C44-932A-75597FAC7913}</c15:txfldGUID>
+                      <c15:txfldGUID>{0FE7EE34-3C3B-4F80-BA06-86FE4EB126E2}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7421,7 +7421,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000032-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7481,7 +7481,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B8C2D83D-17C6-4E76-A66F-65FBDCB5FE2B}</c15:txfldGUID>
+                      <c15:txfldGUID>{E87BBF51-A754-40D3-B40D-A0FF1822201E}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7494,7 +7494,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000033-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7551,7 +7551,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{04FE616D-F946-463B-ADE7-A49FBAD7612E}</c15:txfldGUID>
+                      <c15:txfldGUID>{25FCBFF7-976F-4B0C-B38E-F18FF5E5CCF4}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7561,7 +7561,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000034-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7618,7 +7618,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A0C96378-A7BE-4E37-B746-0B0551BD1B41}</c15:txfldGUID>
+                      <c15:txfldGUID>{0D594862-465F-4F60-B28B-7910D03BE12E}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7628,7 +7628,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000035-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7685,7 +7685,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8DFD5711-A10E-4603-BC72-6C5AE7534383}</c15:txfldGUID>
+                      <c15:txfldGUID>{6868F596-7474-4B46-BE0E-8EF92F3FB84A}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7695,7 +7695,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000036-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7752,7 +7752,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{021F5D5A-8BE0-48F5-91F6-762C29427905}</c15:txfldGUID>
+                      <c15:txfldGUID>{B7F88B50-A29D-440A-9E00-444588181D14}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7762,7 +7762,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000037-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7819,7 +7819,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{71A7C533-904E-4043-9443-5DF6C986D57D}</c15:txfldGUID>
+                      <c15:txfldGUID>{A2C96A11-5D23-4EDA-A4E0-5B84FBC1E070}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7829,7 +7829,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000038-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7886,7 +7886,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E4CC236C-93E2-4863-843B-149B5778EAB7}</c15:txfldGUID>
+                      <c15:txfldGUID>{2D0613BD-CDC1-4915-B544-54A3F7F513B0}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7896,7 +7896,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000039-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7956,7 +7956,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FF175A42-8490-4DD3-A9E4-B696931C8A3F}</c15:txfldGUID>
+                      <c15:txfldGUID>{7EC196A7-B8E2-43A5-B7BB-BD2B279D5BDF}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -7969,7 +7969,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003A-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8029,7 +8029,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5FFEC36E-71D4-4020-B7C2-FE65669B8646}</c15:txfldGUID>
+                      <c15:txfldGUID>{D83EA163-ABEE-447E-A6F4-225A09E5C9EE}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8042,7 +8042,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003B-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8099,7 +8099,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DC6100EB-A6A2-44A8-BF23-A02EFF8769FC}</c15:txfldGUID>
+                      <c15:txfldGUID>{8CA1D7A1-A8C9-4DC4-A4F4-D69A309E10AB}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8109,7 +8109,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003C-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8166,7 +8166,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{03C6BB21-7449-48ED-A68C-FDB14ED7CE73}</c15:txfldGUID>
+                      <c15:txfldGUID>{08EF0117-40BA-492B-B127-B52526057AA9}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8176,7 +8176,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003D-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8233,7 +8233,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A1CAA7EE-122D-4A5B-9897-5C0BA178C612}</c15:txfldGUID>
+                      <c15:txfldGUID>{834718EF-4723-4B3C-969E-0DDCDB1F317B}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8243,7 +8243,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003E-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8300,7 +8300,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{79B9759F-20A6-4D7A-8B83-B406C7968D95}</c15:txfldGUID>
+                      <c15:txfldGUID>{0DA5C52F-31BF-4BA8-924B-B3EE44560D98}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$46</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8310,7 +8310,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000003F-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8488,7 +8488,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000002C-3552-487A-9688-B54672F5703D}"/>
+              <c16:uniqueId val="{0000002C-18F0-48D4-A89B-63A5BC52AF79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8575,7 +8575,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0B0A32BD-0291-4BB4-AD01-1405F62FC4F4}</c15:txfldGUID>
+                      <c15:txfldGUID>{00610C8F-B468-46FC-BB3E-E2FDB74E07C5}</c15:txfldGUID>
                       <c15:f>'C02A'!$B$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8588,7 +8588,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000041-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8646,7 +8646,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D209BFA5-C4AA-4011-8663-A08D070AAAD6}</c15:txfldGUID>
+                      <c15:txfldGUID>{BCAA517E-5502-492B-A303-D63206488E2A}</c15:txfldGUID>
                       <c15:f>'C02A'!$C$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8659,7 +8659,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000042-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8717,7 +8717,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0F54A067-3109-4927-A8AE-3BC8D338F032}</c15:txfldGUID>
+                      <c15:txfldGUID>{54F30EC0-746E-45C8-B6B9-C0BFF3715EBE}</c15:txfldGUID>
                       <c15:f>'C02A'!$D$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8730,7 +8730,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000043-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8788,7 +8788,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C785DDDA-8E67-4D78-B983-31F3D0425AB9}</c15:txfldGUID>
+                      <c15:txfldGUID>{A378C498-A612-4540-9CB5-62F50506670F}</c15:txfldGUID>
                       <c15:f>'C02A'!$E$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8801,7 +8801,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000044-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8859,7 +8859,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CAA2CA2E-005B-4CDA-9DAE-FAA687F1AAC8}</c15:txfldGUID>
+                      <c15:txfldGUID>{1D3CC46C-8DC9-4DB6-AE7E-13712D55E604}</c15:txfldGUID>
                       <c15:f>'C02A'!$F$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8872,7 +8872,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000045-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8930,7 +8930,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{78DD33FB-D4E2-49C5-8424-30D42D049DD6}</c15:txfldGUID>
+                      <c15:txfldGUID>{33A0747A-0C30-4908-ABDF-763E9124EB3D}</c15:txfldGUID>
                       <c15:f>'C02A'!$G$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -8943,7 +8943,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000046-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9001,7 +9001,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{77D6040D-E792-4E5F-B506-8BAFEEA3B9E9}</c15:txfldGUID>
+                      <c15:txfldGUID>{B966C226-FEBE-435F-BB0F-AC4C87F64BFC}</c15:txfldGUID>
                       <c15:f>'C02A'!$H$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9014,7 +9014,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000047-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000047-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9072,7 +9072,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{06433498-61AE-4AE2-B94E-9276AC68DA48}</c15:txfldGUID>
+                      <c15:txfldGUID>{CF99A2D7-FB64-4CA7-93D1-CA9F8824D4FE}</c15:txfldGUID>
                       <c15:f>'C02A'!$I$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9085,7 +9085,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000048-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9143,7 +9143,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{24FE6BA0-B27A-4B34-9B82-641A72D22635}</c15:txfldGUID>
+                      <c15:txfldGUID>{722CF3CF-E05C-49CA-AD6D-8524E1BB3F05}</c15:txfldGUID>
                       <c15:f>'C02A'!$J$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9156,7 +9156,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000049-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9214,7 +9214,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{04501A1B-B250-4759-BFBA-4D9E81B84A3C}</c15:txfldGUID>
+                      <c15:txfldGUID>{C866DC42-C2B2-47B8-B851-CD6ACA1A52BE}</c15:txfldGUID>
                       <c15:f>'C02A'!$K$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9227,7 +9227,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004A-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9285,7 +9285,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BEA0C5AE-1DFD-44B7-95CB-F952B71906B8}</c15:txfldGUID>
+                      <c15:txfldGUID>{C87C2DC2-71E1-4A23-A1D0-8579FD44217F}</c15:txfldGUID>
                       <c15:f>'C02A'!$L$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9298,7 +9298,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004B-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9356,7 +9356,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{19C9157E-01A6-4BA2-9D67-D57E7A6025D0}</c15:txfldGUID>
+                      <c15:txfldGUID>{08CD59D7-FCDB-4C86-8541-CD1E7C34B9F3}</c15:txfldGUID>
                       <c15:f>'C02A'!$M$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9369,7 +9369,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004C-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9427,7 +9427,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BBA03CF7-7E3E-4D5F-B198-B8F4E72D1E9C}</c15:txfldGUID>
+                      <c15:txfldGUID>{86CF6830-4E40-4710-B33E-FB5F45D34C54}</c15:txfldGUID>
                       <c15:f>'C02A'!$N$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9440,7 +9440,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004D-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9498,7 +9498,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3E62F268-ECCE-41AD-8506-ABF662A38539}</c15:txfldGUID>
+                      <c15:txfldGUID>{9C12B780-D502-4799-A2A7-644E60062253}</c15:txfldGUID>
                       <c15:f>'C02A'!$O$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9511,7 +9511,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004E-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9569,7 +9569,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{24E3E0FC-402B-4B9E-9F33-7FEFE3B917F8}</c15:txfldGUID>
+                      <c15:txfldGUID>{2C91E828-FB0B-4CEE-882F-392D8F1E7BB1}</c15:txfldGUID>
                       <c15:f>'C02A'!$P$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9582,7 +9582,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004F-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{0000004F-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9640,7 +9640,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BE69559F-B1B4-4652-82E1-F177766312DF}</c15:txfldGUID>
+                      <c15:txfldGUID>{0E9575CC-7818-41D9-8398-B1F3FCE9DA2E}</c15:txfldGUID>
                       <c15:f>'C02A'!$Q$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9653,7 +9653,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000050-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000050-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9711,7 +9711,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9D6DA6FA-2497-45D2-AFC8-13BE98F9FB3C}</c15:txfldGUID>
+                      <c15:txfldGUID>{725C8D5A-FBAD-4FAC-853B-C78875086E2D}</c15:txfldGUID>
                       <c15:f>'C02A'!$R$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9724,7 +9724,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000051-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000051-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9782,7 +9782,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CAA61358-FDCD-42AA-AE55-68E2F4B7D472}</c15:txfldGUID>
+                      <c15:txfldGUID>{EDD3BFA4-A181-494D-998E-D0C197F42F4C}</c15:txfldGUID>
                       <c15:f>'C02A'!$S$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9795,7 +9795,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000052-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000052-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9853,7 +9853,7 @@
                   </c15:spPr>
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{172AE0A3-2374-483B-88E4-EC9B478ABB93}</c15:txfldGUID>
+                      <c15:txfldGUID>{0B0E7184-5789-44C5-99D5-7709FBEAB917}</c15:txfldGUID>
                       <c15:f>'C02A'!$T$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -9866,7 +9866,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000053-3552-487A-9688-B54672F5703D}"/>
+                  <c16:uniqueId val="{00000053-18F0-48D4-A89B-63A5BC52AF79}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10037,7 +10037,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000040-3552-487A-9688-B54672F5703D}"/>
+              <c16:uniqueId val="{00000040-18F0-48D4-A89B-63A5BC52AF79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10051,11 +10051,11 @@
         </c:dLbls>
         <c:gapWidth val="26"/>
         <c:overlap val="100"/>
-        <c:axId val="1414523695"/>
-        <c:axId val="1419163215"/>
+        <c:axId val="2062542064"/>
+        <c:axId val="1098028400"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1414523695"/>
+        <c:axId val="2062542064"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -10079,7 +10079,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419163215"/>
+        <c:crossAx val="1098028400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10087,7 +10087,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419163215"/>
+        <c:axId val="1098028400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0080645161290323"/>
@@ -10121,7 +10121,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1414523695"/>
+        <c:crossAx val="2062542064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10335,7 +10335,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-B66A-4A4A-8097-E2382FDAD8FF}"/>
+              <c16:uniqueId val="{00000007-4910-48D3-8EB2-D8680DEF496C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10384,7 +10384,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                <c16:uniqueId val="{00000009-4910-48D3-8EB2-D8680DEF496C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10410,7 +10410,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000A-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                <c16:uniqueId val="{0000000A-4910-48D3-8EB2-D8680DEF496C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10436,7 +10436,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                <c16:uniqueId val="{0000000B-4910-48D3-8EB2-D8680DEF496C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10465,7 +10465,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6388DB49-F361-47D3-A938-423D4AB54E7E}</c15:txfldGUID>
+                      <c15:txfldGUID>{11E2F7E0-5A07-4C38-82F5-1C81E4C92C85}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10478,7 +10478,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000C-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10506,7 +10506,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{85043289-D0A0-4CD9-94DE-9566318E77DD}</c15:txfldGUID>
+                      <c15:txfldGUID>{3E81DC9E-A946-4CCE-87CF-C2E84DD64299}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10519,7 +10519,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000D-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10547,7 +10547,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EDE78505-8AEB-440C-97EF-98BC1CFBF230}</c15:txfldGUID>
+                      <c15:txfldGUID>{C9282B58-C3E7-479E-9E38-E112C2C42FEE}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10560,7 +10560,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000E-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10588,7 +10588,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{7379B32C-237B-4416-8901-7BA73D198C2B}</c15:txfldGUID>
+                      <c15:txfldGUID>{F268AFB2-5975-41CE-8FEE-F9F8863A0A13}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10601,7 +10601,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000F-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10629,7 +10629,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BDDB8AAF-7A0D-41A0-947A-2D4B3A317873}</c15:txfldGUID>
+                      <c15:txfldGUID>{3316B3A1-5B79-45AA-8A27-54F565A5CA1C}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10642,7 +10642,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000010-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10670,7 +10670,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ABB447AB-3F1B-4DC5-8F74-E747A33F51CD}</c15:txfldGUID>
+                      <c15:txfldGUID>{157263A2-BA1E-4526-8AB3-C7AE1ED7952C}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10683,7 +10683,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000011-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10711,7 +10711,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A189777D-2C97-4991-AA7D-6E153C8F8073}</c15:txfldGUID>
+                      <c15:txfldGUID>{AE15E0FD-F537-46D4-B8BA-57E889E2A63C}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10724,7 +10724,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000012-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10752,7 +10752,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F678C6DA-F447-4E5D-9C6B-B550822FC4F6}</c15:txfldGUID>
+                      <c15:txfldGUID>{61BD408B-8349-4299-A491-E3BE75182DC9}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10765,7 +10765,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000013-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10793,7 +10793,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3D3246BA-351C-4734-8DF3-194F68B12DBB}</c15:txfldGUID>
+                      <c15:txfldGUID>{C05F7425-324F-4ADC-A458-3CDDCB22C503}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10806,7 +10806,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000014-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10834,7 +10834,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FA071ABB-AC41-4264-AC56-F61C62A8A5F1}</c15:txfldGUID>
+                      <c15:txfldGUID>{190A072A-096B-45EF-B1FB-356E230FA309}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10847,7 +10847,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{00000009-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10875,7 +10875,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E9802C9A-2A1B-4EF8-8C23-A99BBF457D12}</c15:txfldGUID>
+                      <c15:txfldGUID>{E315EA91-8E38-4DC9-B559-02AA61B39B87}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10888,7 +10888,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000A-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10916,7 +10916,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3308C515-51B7-4A33-A589-C8093E4D2FF8}</c15:txfldGUID>
+                      <c15:txfldGUID>{D5AF87B5-873B-429B-A1D2-68B58EF15B72}</c15:txfldGUID>
                       <c15:f>'C03A'!$S$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -10929,7 +10929,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-B66A-4A4A-8097-E2382FDAD8FF}"/>
+                  <c16:uniqueId val="{0000000B-4910-48D3-8EB2-D8680DEF496C}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11062,7 +11062,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-B66A-4A4A-8097-E2382FDAD8FF}"/>
+              <c16:uniqueId val="{00000008-4910-48D3-8EB2-D8680DEF496C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11076,11 +11076,11 @@
         </c:dLbls>
         <c:gapWidth val="23"/>
         <c:overlap val="76"/>
-        <c:axId val="1433942799"/>
-        <c:axId val="1419202575"/>
+        <c:axId val="2062819120"/>
+        <c:axId val="1098059600"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1433942799"/>
+        <c:axId val="2062819120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11104,7 +11104,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419202575"/>
+        <c:crossAx val="1098059600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11112,7 +11112,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419202575"/>
+        <c:axId val="1098059600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0900473933649288"/>
@@ -11146,7 +11146,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1433942799"/>
+        <c:crossAx val="2062819120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11401,7 +11401,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+              <c16:uniqueId val="{00000007-4883-49A4-A322-D3F3F51B62E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11453,7 +11453,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F0D78E08-0D33-4706-AF5E-B4DB5679FE26}</c15:txfldGUID>
+                      <c15:txfldGUID>{A57A9116-6727-4AD2-A176-8D524E0AAEA0}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11466,7 +11466,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000009-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11494,7 +11494,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F87DA228-4EEA-40E2-A75C-CC0F2604E1B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{34E243A1-A30D-493A-B816-D0614911C132}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11507,7 +11507,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000A-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11535,7 +11535,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AC7CF271-13C0-484E-BB0F-ACB8DFC3CDA0}</c15:txfldGUID>
+                      <c15:txfldGUID>{6FBD040C-E5F9-4B62-8EB1-B30F11FE6A45}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11548,7 +11548,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000B-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11576,7 +11576,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{84E09DAC-264E-4221-A0B2-37B3B4E28132}</c15:txfldGUID>
+                      <c15:txfldGUID>{0B57067C-DEBF-4319-95ED-0DF63189C502}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11589,7 +11589,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000C-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11617,7 +11617,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D7723355-2DA0-48DC-A8C1-F69E7D303B7A}</c15:txfldGUID>
+                      <c15:txfldGUID>{47F4034F-7AE9-462C-94D1-00CC100605C3}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11630,7 +11630,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000D-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11658,7 +11658,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{28E181CD-643E-4B5D-AEAA-00112AE8298F}</c15:txfldGUID>
+                      <c15:txfldGUID>{5519290A-AFD3-4429-9633-4AA7DFC885FF}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11671,7 +11671,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000E-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11699,7 +11699,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{39BDD97B-193B-4B28-84AD-7294560E26B5}</c15:txfldGUID>
+                      <c15:txfldGUID>{AC4A1861-0801-44EE-8363-C92D2C030325}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11712,7 +11712,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000000F-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11740,7 +11740,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{39C51DAB-528F-455E-98BE-02785CE80455}</c15:txfldGUID>
+                      <c15:txfldGUID>{61CC6A04-D923-4B80-8225-0FFCC9A3E561}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11753,7 +11753,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000010-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11781,7 +11781,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{64A243F4-9B70-4891-A45C-5688F34D192C}</c15:txfldGUID>
+                      <c15:txfldGUID>{1ACC5BB6-1C92-4E7F-913F-7F44DC5AB7E4}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11794,7 +11794,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000011-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11822,7 +11822,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A929D5DC-02EC-4F8C-8D39-E5C5427D8CB0}</c15:txfldGUID>
+                      <c15:txfldGUID>{0FE642ED-C78D-4AC9-959B-4B223C4288B8}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11835,7 +11835,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000012-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11863,7 +11863,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{1797CAFD-1E7C-44D5-9A33-F95E6336A631}</c15:txfldGUID>
+                      <c15:txfldGUID>{C1579339-3519-4275-AB09-068C7F373C2D}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11876,7 +11876,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000013-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11904,7 +11904,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{73C4AB41-FD24-431F-AEDE-9A17DE132E96}</c15:txfldGUID>
+                      <c15:txfldGUID>{21271C41-2DA9-4FB4-87CE-EAE14DB0E6A9}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11917,7 +11917,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000014-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11945,7 +11945,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{75B49C45-E360-4177-8F5D-AF3A1068BCAA}</c15:txfldGUID>
+                      <c15:txfldGUID>{F84B4F75-08EE-45B9-AA45-BE8BF9984ED7}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11958,7 +11958,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000015-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11986,7 +11986,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D833D7F7-956F-47FB-A900-549070746AB6}</c15:txfldGUID>
+                      <c15:txfldGUID>{8E7CCFFD-2E71-4A31-B448-C115D88C11AE}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -11999,7 +11999,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000016-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12027,7 +12027,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5AD75807-E24F-4BB2-940A-A653CB82A069}</c15:txfldGUID>
+                      <c15:txfldGUID>{57617FA2-CADE-4E03-A463-432AD9C47A53}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12040,7 +12040,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000017-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12068,7 +12068,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9B147565-8207-4007-9FB1-CDA633313911}</c15:txfldGUID>
+                      <c15:txfldGUID>{08BA0372-A532-45FD-8DDA-5B1FB943BB98}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12081,7 +12081,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000018-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12109,7 +12109,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{26BFCBA4-BAA4-4EC1-A650-4C5FBA8945A8}</c15:txfldGUID>
+                      <c15:txfldGUID>{FB32467D-341B-42EE-AA00-07D6A1222C0E}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12122,7 +12122,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{00000019-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12150,7 +12150,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E2A923F7-3D88-4F99-88D4-5E8F97945E2D}</c15:txfldGUID>
+                      <c15:txfldGUID>{9ADD5BBD-12E9-49DD-AE92-392BE7A6CCC3}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12163,7 +12163,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000001A-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12191,7 +12191,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E44D2E9D-A8C8-48B9-A9EC-9166BC432B43}</c15:txfldGUID>
+                      <c15:txfldGUID>{9A15A8BF-5841-44B5-B2D2-D794BAA09526}</c15:txfldGUID>
                       <c15:f>'C04A'!$Q$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12204,7 +12204,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+                  <c16:uniqueId val="{0000001B-4883-49A4-A322-D3F3F51B62E7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12379,7 +12379,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-56DB-40F6-8AC4-8DFD34D70D8C}"/>
+              <c16:uniqueId val="{00000008-4883-49A4-A322-D3F3F51B62E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12393,11 +12393,11 @@
         </c:dLbls>
         <c:gapWidth val="20"/>
         <c:overlap val="76"/>
-        <c:axId val="1437190159"/>
-        <c:axId val="1419251535"/>
+        <c:axId val="1184792160"/>
+        <c:axId val="1098098000"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1437190159"/>
+        <c:axId val="1184792160"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -12421,7 +12421,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419251535"/>
+        <c:crossAx val="1098098000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12429,7 +12429,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419251535"/>
+        <c:axId val="1098098000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.095890410958904"/>
@@ -12463,7 +12463,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1437190159"/>
+        <c:crossAx val="1184792160"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12717,7 +12717,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+              <c16:uniqueId val="{00000007-F131-4AF1-9933-903A0ADA8CFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12751,7 +12751,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000009-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12761,7 +12761,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000A-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12789,7 +12789,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ACD3A331-042F-4F98-BE2C-DC4B858E6613}</c15:txfldGUID>
+                      <c15:txfldGUID>{87D266CD-366A-44FB-B92B-A9B2C1D16B83}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12802,7 +12802,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000B-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12830,7 +12830,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C24CB419-0E3A-4FAC-942B-B6D9126DADB1}</c15:txfldGUID>
+                      <c15:txfldGUID>{8C2A1C2E-94A7-4839-BF10-E696D3D4714F}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12843,7 +12843,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000C-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12871,7 +12871,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{408E7D66-1EC4-4F90-8ED7-6E3DBE96FBC7}</c15:txfldGUID>
+                      <c15:txfldGUID>{FEF9843E-A557-4450-93FA-368EFE6A8E89}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -12884,7 +12884,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000D-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12894,7 +12894,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000E-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12904,7 +12904,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000000F-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12914,7 +12914,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000010-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12924,7 +12924,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000011-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12934,7 +12934,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000012-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12944,7 +12944,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000013-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12954,7 +12954,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000014-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12964,7 +12964,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000015-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12974,7 +12974,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000016-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12984,7 +12984,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000017-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13012,7 +13012,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F3381031-D6BD-41C7-8A89-75789890D08A}</c15:txfldGUID>
+                      <c15:txfldGUID>{80BFA1D7-6B00-46CD-B725-12B79BF69312}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13025,7 +13025,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000018-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13053,7 +13053,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F2ABE12B-D1D7-43D6-8E0F-EFA162BE4996}</c15:txfldGUID>
+                      <c15:txfldGUID>{22CF64FD-78E7-48ED-91A9-0D12E34662E2}</c15:txfldGUID>
                       <c15:f>'C05X'!$AI$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13066,7 +13066,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000019-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13229,7 +13229,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+              <c16:uniqueId val="{00000008-F131-4AF1-9933-903A0ADA8CFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13263,7 +13263,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000001B-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13273,7 +13273,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000001C-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13283,7 +13283,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000001D-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13293,7 +13293,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000001E-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13303,7 +13303,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000001F-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13331,7 +13331,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E8BC8678-3AC9-46B3-AA70-6CA05525B9DC}</c15:txfldGUID>
+                      <c15:txfldGUID>{272D7830-5D76-484F-B128-570792CA6084}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13344,7 +13344,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000020-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13372,7 +13372,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{68F4E08F-77B4-4968-AEEE-71E2714DA681}</c15:txfldGUID>
+                      <c15:txfldGUID>{F53CE98E-9764-43F5-8293-1F84323330FE}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13385,7 +13385,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000021-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13413,7 +13413,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BA0641DB-D474-41ED-8F1D-93341D1C4A7F}</c15:txfldGUID>
+                      <c15:txfldGUID>{5CDA238A-19B4-4550-A962-6F6E2ABF7233}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13426,7 +13426,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000022-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13454,7 +13454,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E58B0F66-6AE5-4316-95D3-C147D03412F4}</c15:txfldGUID>
+                      <c15:txfldGUID>{BF84D153-5A64-4C39-BBA5-CD92D85FACA6}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13467,7 +13467,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000023-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13495,7 +13495,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{40A8FA9B-3CF7-4DCA-A731-916C37A712A3}</c15:txfldGUID>
+                      <c15:txfldGUID>{6AC6CACA-CD47-4AC2-B700-948BC2DB1E50}</c15:txfldGUID>
                       <c15:f>'C05X'!$AK$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13508,7 +13508,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000024-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13518,7 +13518,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000025-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13528,7 +13528,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000026-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13538,7 +13538,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000027-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13548,7 +13548,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000028-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13558,7 +13558,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000029-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13568,7 +13568,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000002A-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13578,7 +13578,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000002B-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13741,7 +13741,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001A-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+              <c16:uniqueId val="{0000001A-F131-4AF1-9933-903A0ADA8CFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13774,7 +13774,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000002D-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13784,7 +13784,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000002E-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13794,7 +13794,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000002F-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13804,7 +13804,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000030-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13814,7 +13814,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000031-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13824,7 +13824,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000032-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13834,7 +13834,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000033-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13844,7 +13844,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000034-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13854,7 +13854,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000035-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13864,7 +13864,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000036-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13892,7 +13892,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9F15186E-F38E-4143-9BF7-CE7211FB28EE}</c15:txfldGUID>
+                      <c15:txfldGUID>{CCF6EEB5-F990-48DA-A58D-CB2CBD1C950D}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13905,7 +13905,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000037-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13933,7 +13933,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A740A4F0-47DD-4D34-87EA-6E433E85357A}</c15:txfldGUID>
+                      <c15:txfldGUID>{1FDDB926-B696-4543-942A-FF5D5FD82676}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13946,7 +13946,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000038-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -13974,7 +13974,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{170336FA-734F-4244-9F68-5761BA7D54A2}</c15:txfldGUID>
+                      <c15:txfldGUID>{9CDC92CC-98EE-4C06-AB67-2F2DA6DD4DD1}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -13987,7 +13987,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{00000039-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14015,7 +14015,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F9FCBD20-05C1-4DC2-8016-91FB4011EA79}</c15:txfldGUID>
+                      <c15:txfldGUID>{FC3F477B-AF8A-41BF-98DB-60F5F01F20F6}</c15:txfldGUID>
                       <c15:f>'C05X'!$AM$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14028,7 +14028,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000003A-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14038,7 +14038,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000003B-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14048,7 +14048,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000003C-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14058,7 +14058,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+                  <c16:uniqueId val="{0000003D-F131-4AF1-9933-903A0ADA8CFD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14221,7 +14221,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000002C-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+              <c16:uniqueId val="{0000002C-F131-4AF1-9933-903A0ADA8CFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14368,7 +14368,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000003E-F7BF-4A33-839B-8DA8BEBD49D1}"/>
+              <c16:uniqueId val="{0000003E-F131-4AF1-9933-903A0ADA8CFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14382,11 +14382,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="1437174847"/>
-        <c:axId val="1419077775"/>
+        <c:axId val="2062816336"/>
+        <c:axId val="1098117200"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1437174847"/>
+        <c:axId val="2062816336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14432,7 +14432,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419077775"/>
+        <c:crossAx val="1098117200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14440,7 +14440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419077775"/>
+        <c:axId val="1098117200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.1494252873563218"/>
@@ -14474,7 +14474,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="1437174847"/>
+        <c:crossAx val="2062816336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14627,7 +14627,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C90652B2-5B99-459F-8C6B-7994DF8E6CB6}</c15:txfldGUID>
+                      <c15:txfldGUID>{43369391-81B9-4962-845D-0CAC19A00476}</c15:txfldGUID>
                       <c15:f>'C05X'!$Z$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -14640,7 +14640,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000008-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14650,7 +14650,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000009-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14660,7 +14660,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000A-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14670,7 +14670,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000B-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14680,7 +14680,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000C-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14690,7 +14690,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000D-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14700,7 +14700,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000E-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14710,7 +14710,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000000F-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14720,7 +14720,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000010-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14730,7 +14730,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000011-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14740,7 +14740,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000012-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14750,7 +14750,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000013-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14760,7 +14760,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000014-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14770,7 +14770,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000015-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14780,7 +14780,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000016-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14790,7 +14790,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000017-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14800,7 +14800,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000018-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -14963,7 +14963,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-2511-4876-B14E-A04059A972AB}"/>
+              <c16:uniqueId val="{00000007-F559-4268-87B7-E821E82FFB18}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14991,7 +14991,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001A-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15019,7 +15019,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ABE20B2B-C87D-40C3-9AC3-6989A9F34A82}</c15:txfldGUID>
+                      <c15:txfldGUID>{5042FF0E-70FC-41BA-9443-D6252D820F4C}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15032,7 +15032,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001B-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15060,7 +15060,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5771520D-58BD-4295-8876-E3DDB5470233}</c15:txfldGUID>
+                      <c15:txfldGUID>{356F6249-E20B-496A-8B2F-0D0EA3DD5F70}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15073,7 +15073,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001C-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15101,7 +15101,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{123FCC02-0294-4ECA-B569-B9E5ACA40326}</c15:txfldGUID>
+                      <c15:txfldGUID>{F6F40BE4-67A7-429F-AD9E-F2C2281C5EF8}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15114,7 +15114,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001D-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15142,7 +15142,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F3E2FA79-7179-4E6C-AFAA-0C19873959F0}</c15:txfldGUID>
+                      <c15:txfldGUID>{FE1EEBD4-B23B-4E3E-AAF8-62C77B04C4C8}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15155,7 +15155,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001E-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15183,7 +15183,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{43C0D579-B9EC-4498-9F68-EEB3370DA21D}</c15:txfldGUID>
+                      <c15:txfldGUID>{302E5392-D2B2-412A-911A-7451BE826199}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15196,7 +15196,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000001F-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15224,7 +15224,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{491812B0-11E1-4C01-83AD-D92B47F3FE3B}</c15:txfldGUID>
+                      <c15:txfldGUID>{0ADD8C1F-2F3C-4ECF-9EC2-F0593D8C160A}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15237,7 +15237,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000020-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15265,7 +15265,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9A021FCA-4749-4D66-93F2-A2E31BE7B0FB}</c15:txfldGUID>
+                      <c15:txfldGUID>{6AFAC960-7EB7-486B-A6B7-89CB18255FDD}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15278,7 +15278,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000021-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15306,7 +15306,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9C3D8F99-5791-440F-8EBD-2AB1C12DC378}</c15:txfldGUID>
+                      <c15:txfldGUID>{F29B0D50-23C6-4EFB-82B4-3E52A7127037}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15319,7 +15319,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000022-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15347,7 +15347,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B5BDA612-7C1D-43D7-85FA-167CEACE262B}</c15:txfldGUID>
+                      <c15:txfldGUID>{DE731753-8CA7-4908-BA5B-B7A83527A606}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15360,7 +15360,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000023-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15388,7 +15388,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{11F5BBA0-CB95-477A-8FE1-BE30EC476E9B}</c15:txfldGUID>
+                      <c15:txfldGUID>{ED6654B3-B049-441D-A31B-47440E61F82A}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15401,7 +15401,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000024-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15429,7 +15429,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{75AB957B-DC2C-4FB9-B30D-015C1A006954}</c15:txfldGUID>
+                      <c15:txfldGUID>{CC6B11C6-B5A0-4908-8C4F-77FE9DFBBC42}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15442,7 +15442,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000025-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15470,7 +15470,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{811B924F-3FC0-41AE-AB84-E40B8A56014B}</c15:txfldGUID>
+                      <c15:txfldGUID>{0FF28FD0-3F8D-4B4A-A8C4-D8C3C2D2B72D}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15483,7 +15483,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000026-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15511,7 +15511,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6C7B1D28-9779-4699-8BF4-CAD65B8FBCE2}</c15:txfldGUID>
+                      <c15:txfldGUID>{D158FC01-EAB6-4133-9141-045F6E2D9999}</c15:txfldGUID>
                       <c15:f>'C05X'!$AB$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15524,7 +15524,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000027-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15534,7 +15534,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000028-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15544,7 +15544,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000029-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15554,7 +15554,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000002A-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15717,7 +15717,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000019-2511-4876-B14E-A04059A972AB}"/>
+              <c16:uniqueId val="{00000019-F559-4268-87B7-E821E82FFB18}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15751,7 +15751,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000002C-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15761,7 +15761,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000002D-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15789,7 +15789,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5E976820-A6AD-4A98-B908-8B806DB9A3EE}</c15:txfldGUID>
+                      <c15:txfldGUID>{8A475EC3-B1A0-4A64-82AA-1213F44F1130}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15802,7 +15802,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000002E-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15830,7 +15830,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0B14CA9A-2DB0-40AB-8A18-418AC7300F7B}</c15:txfldGUID>
+                      <c15:txfldGUID>{C5694650-FD6A-4728-917B-7FBA64D8AF2F}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15843,7 +15843,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000002F-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15871,7 +15871,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6F9C3ADC-A071-4F48-81C0-20FC934438FA}</c15:txfldGUID>
+                      <c15:txfldGUID>{D0E7B6F0-61F3-4D13-88B3-98C6EDF342A6}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15884,7 +15884,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000030-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15912,7 +15912,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C7F81110-33E4-49B4-B48A-50007EFE4862}</c15:txfldGUID>
+                      <c15:txfldGUID>{F6617ECA-5D06-4CF6-B709-1C2FE97E5139}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15925,7 +15925,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000031-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15953,7 +15953,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6B545021-7978-44D3-90E9-A7CC1D109A0C}</c15:txfldGUID>
+                      <c15:txfldGUID>{35A218D5-046A-47CD-8C8C-5BD0B7B641EF}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -15966,7 +15966,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000032-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15994,7 +15994,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{77D4E436-5A40-49FD-8903-9A7696EA212E}</c15:txfldGUID>
+                      <c15:txfldGUID>{A71CB79C-B964-4C63-94C7-66D7D353A540}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16007,7 +16007,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000033-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16035,7 +16035,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5AA95FBB-39C0-4756-AE97-F84818479B9C}</c15:txfldGUID>
+                      <c15:txfldGUID>{326627B4-EE3F-42AF-94D6-1F625D4BC6DD}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16048,7 +16048,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000034-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16076,7 +16076,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3961F186-F1BE-4413-A10F-7899D56C3E76}</c15:txfldGUID>
+                      <c15:txfldGUID>{3D6FCD2E-5CA2-42E5-A51D-015D424E7AB0}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16089,7 +16089,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000035-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16099,7 +16099,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000036-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16109,7 +16109,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000037-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16119,7 +16119,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000038-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16129,7 +16129,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000039-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16157,7 +16157,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{98C67514-C96C-40D7-B48C-55A4DEF9575E}</c15:txfldGUID>
+                      <c15:txfldGUID>{0D5ADAC8-E780-4539-AF0C-B77FAE08B613}</c15:txfldGUID>
                       <c15:f>'C05X'!$AD$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16170,7 +16170,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000003A-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16180,7 +16180,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000003B-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16190,7 +16190,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000003C-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16353,7 +16353,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000002B-2511-4876-B14E-A04059A972AB}"/>
+              <c16:uniqueId val="{0000002B-F559-4268-87B7-E821E82FFB18}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16386,7 +16386,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000003E-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16396,7 +16396,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000003F-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16406,7 +16406,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000040-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000040-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16416,7 +16416,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000041-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16426,7 +16426,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000042-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16436,7 +16436,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000043-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16446,7 +16446,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000044-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16456,7 +16456,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000045-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16466,7 +16466,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000046-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16476,7 +16476,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000047-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000047-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16504,7 +16504,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A91E551C-07FC-46DB-888F-4530E52C2917}</c15:txfldGUID>
+                      <c15:txfldGUID>{98B93B0C-F50D-4F1B-97E6-F0AF93F3DFB4}</c15:txfldGUID>
                       <c15:f>'C05X'!$AF$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16517,7 +16517,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000048-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16545,7 +16545,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BD8A569D-1D41-4D4A-8E08-BCB2C06C86E9}</c15:txfldGUID>
+                      <c15:txfldGUID>{911AF820-A0B9-4521-9B9A-EE765E21EC22}</c15:txfldGUID>
                       <c15:f>'C05X'!$AF$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16558,7 +16558,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{00000049-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16586,7 +16586,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{43E637D4-846A-4EC3-929D-CE09F45D8F83}</c15:txfldGUID>
+                      <c15:txfldGUID>{555E21E5-8527-4083-B373-769AC8CB1821}</c15:txfldGUID>
                       <c15:f>'C05X'!$AF$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16599,7 +16599,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000004A-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16627,7 +16627,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{54FC74BD-867D-4C75-BC52-3180A5B0D9E6}</c15:txfldGUID>
+                      <c15:txfldGUID>{D5C705BE-1CA1-4C21-B185-EA1B04034CA5}</c15:txfldGUID>
                       <c15:f>'C05X'!$AF$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16640,7 +16640,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000004B-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16668,7 +16668,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{95625BB8-CF6F-42E0-AA97-372E8CC955FD}</c15:txfldGUID>
+                      <c15:txfldGUID>{FE23D2CB-687C-4658-89BE-7C8AAF247739}</c15:txfldGUID>
                       <c15:f>'C05X'!$AF$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -16681,7 +16681,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000004C-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16691,7 +16691,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000004D-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16701,7 +16701,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-2511-4876-B14E-A04059A972AB}"/>
+                  <c16:uniqueId val="{0000004E-F559-4268-87B7-E821E82FFB18}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -16864,7 +16864,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000003D-2511-4876-B14E-A04059A972AB}"/>
+              <c16:uniqueId val="{0000003D-F559-4268-87B7-E821E82FFB18}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16878,11 +16878,11 @@
         </c:dLbls>
         <c:gapWidth val="40"/>
         <c:overlap val="76"/>
-        <c:axId val="889680527"/>
-        <c:axId val="1419082095"/>
+        <c:axId val="1212141696"/>
+        <c:axId val="1098116720"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="889680527"/>
+        <c:axId val="1212141696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16892,7 +16892,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="1419082095"/>
+        <c:crossAx val="1098116720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16900,7 +16900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419082095"/>
+        <c:axId val="1098116720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.1494252873563218"/>
@@ -16934,7 +16934,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="889680527"/>
+        <c:crossAx val="1212141696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17069,7 +17069,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000008-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17079,7 +17079,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000009-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17107,7 +17107,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0724FF45-A43F-4832-90E9-B5F872CDA6AC}</c15:txfldGUID>
+                      <c15:txfldGUID>{C6ED1605-D7FF-4A0F-9622-E26A2B07E159}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17120,7 +17120,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17148,7 +17148,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E99E6A72-A70E-4910-8D16-28D2C135CB04}</c15:txfldGUID>
+                      <c15:txfldGUID>{68D27437-D4BC-4141-84F1-5B9CCA363E25}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17161,7 +17161,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17189,7 +17189,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F0822406-CEA6-4682-AD3C-7BA03EC2B7EE}</c15:txfldGUID>
+                      <c15:txfldGUID>{8D5E126C-A684-43EA-B815-EC7B568BE59F}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17202,7 +17202,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000C-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17230,7 +17230,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{77478E7C-99F3-4B0A-9E42-EADC0C065B61}</c15:txfldGUID>
+                      <c15:txfldGUID>{A6B8968B-3EB8-473A-A6D2-2474755908A8}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17243,7 +17243,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000D-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17271,7 +17271,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9885F12F-8711-4EDD-B263-4BCE8F3889A1}</c15:txfldGUID>
+                      <c15:txfldGUID>{F0C57566-2837-4C77-8353-A724103749D5}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17284,7 +17284,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000E-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17312,7 +17312,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ED0E95BB-E9F6-4063-A28D-3A95C7BE50C0}</c15:txfldGUID>
+                      <c15:txfldGUID>{62178A0D-4C12-4ED4-AC5F-34C35AD3A8CB}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17325,7 +17325,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000000F-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17353,7 +17353,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D5C74558-64C8-4BCB-A896-2F63E9B6F96E}</c15:txfldGUID>
+                      <c15:txfldGUID>{DE3EB4AA-7A78-4A95-B968-AD99E550581E}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17366,7 +17366,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000010-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17394,7 +17394,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A95CEDD8-A062-4B39-A328-7976894AF5B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{07FBAF1A-7698-4103-849E-860F3A7945BE}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17407,7 +17407,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000011-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17435,7 +17435,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4AF662D8-0D79-4688-964B-AC256361C130}</c15:txfldGUID>
+                      <c15:txfldGUID>{5BFE191C-D062-4D9F-9219-7F74552BC29B}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17448,7 +17448,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000012-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17476,7 +17476,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A850C9FC-87F6-4876-B1BD-261B5EB20C96}</c15:txfldGUID>
+                      <c15:txfldGUID>{8AEF38A4-1385-477A-98DA-86C6B89DC65C}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17489,7 +17489,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000013-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17517,7 +17517,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{14C8B684-B397-4732-ACE7-102DCA3585F9}</c15:txfldGUID>
+                      <c15:txfldGUID>{632B813A-23DF-4D28-988F-B8A6EE5811F0}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17530,7 +17530,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000014-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17558,7 +17558,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A9B99172-ADE5-4B2D-AD10-F3F172FE2AF3}</c15:txfldGUID>
+                      <c15:txfldGUID>{13212690-5AC9-4A13-89FC-724F398A2378}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17571,7 +17571,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000015-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17599,7 +17599,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{133BE0C0-16BF-4F10-90F5-1E792693C0C3}</c15:txfldGUID>
+                      <c15:txfldGUID>{3F65805E-E41F-45DF-A696-27257168F39B}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17612,7 +17612,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000016-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17640,7 +17640,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{A3F300C0-B0B5-47A5-B277-8758FE7A3976}</c15:txfldGUID>
+                      <c15:txfldGUID>{0B316C15-0CC1-4AAA-9305-F6AE8B7E7591}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17653,7 +17653,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000017-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17681,7 +17681,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B07EB92F-CA9C-4376-87E2-69B5C39B1498}</c15:txfldGUID>
+                      <c15:txfldGUID>{B0693471-CD09-4CEF-9B80-A6331BF2F945}</c15:txfldGUID>
                       <c15:f>'C06F'!$W$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -17694,7 +17694,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000018-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17704,7 +17704,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000019-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17714,7 +17714,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000001A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17724,7 +17724,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000001B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -17905,7 +17905,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-9759-48B7-BA79-3459BD31F5C4}"/>
+              <c16:uniqueId val="{00000007-CEC7-4370-A398-389D1CDAFA69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18071,7 +18071,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001C-9759-48B7-BA79-3459BD31F5C4}"/>
+              <c16:uniqueId val="{0000001C-CEC7-4370-A398-389D1CDAFA69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18117,7 +18117,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{CCD9D6A5-1484-479F-8130-DDD2C76E9973}</c15:txfldGUID>
+                      <c15:txfldGUID>{CBF774DF-2166-44C3-A0F6-F7E50524577F}</c15:txfldGUID>
                       <c15:f>'C06F'!$Z$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18130,7 +18130,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000001E-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18140,7 +18140,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000001F-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18150,7 +18150,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000020-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18160,7 +18160,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000021-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18170,7 +18170,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000022-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18180,7 +18180,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000023-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18190,7 +18190,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000024-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18200,7 +18200,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000025-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18210,7 +18210,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000026-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18220,7 +18220,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000027-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18230,7 +18230,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000028-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18240,7 +18240,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000029-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18250,7 +18250,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18260,7 +18260,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18270,7 +18270,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002C-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18280,7 +18280,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002D-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18290,7 +18290,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002E-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18300,7 +18300,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000002F-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18310,7 +18310,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000030-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18320,7 +18320,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000031-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18501,7 +18501,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-9759-48B7-BA79-3459BD31F5C4}"/>
+              <c16:uniqueId val="{0000001D-CEC7-4370-A398-389D1CDAFA69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18535,7 +18535,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000033-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18563,7 +18563,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{85DF3E5D-653E-4C93-9AF9-43BC10923427}</c15:txfldGUID>
+                      <c15:txfldGUID>{77B261FD-DA82-4BD9-B95C-5608F694A194}</c15:txfldGUID>
                       <c15:f>'C06F'!$AB$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -18576,7 +18576,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000034-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18586,7 +18586,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000035-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18596,7 +18596,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000036-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18606,7 +18606,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000037-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18616,7 +18616,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000038-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18626,7 +18626,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000039-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18636,7 +18636,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18646,7 +18646,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18656,7 +18656,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003C-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18666,7 +18666,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003D-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18676,7 +18676,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003E-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18686,7 +18686,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000003F-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18696,7 +18696,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000040-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000040-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18706,7 +18706,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000041-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18716,7 +18716,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000042-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18726,7 +18726,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000043-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18736,7 +18736,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000044-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18746,7 +18746,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000045-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18756,7 +18756,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000046-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18937,7 +18937,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000032-9759-48B7-BA79-3459BD31F5C4}"/>
+              <c16:uniqueId val="{00000032-CEC7-4370-A398-389D1CDAFA69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18971,7 +18971,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000048-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18981,7 +18981,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000049-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -18991,7 +18991,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19001,7 +19001,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19011,7 +19011,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004C-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19021,7 +19021,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004D-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19031,7 +19031,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004E-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19041,7 +19041,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004F-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000004F-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19051,7 +19051,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000050-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000050-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19061,7 +19061,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000051-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000051-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19071,7 +19071,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000052-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000052-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19081,7 +19081,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000053-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000053-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19091,7 +19091,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000054-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000054-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19101,7 +19101,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000055-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000055-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19111,7 +19111,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000056-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000056-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19121,7 +19121,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000057-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000057-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19131,7 +19131,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000058-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000058-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19159,7 +19159,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BAAC9B58-5A37-4CA3-9A4C-760929C521E4}</c15:txfldGUID>
+                      <c15:txfldGUID>{A1DF4AEB-CEC1-4070-9300-99E598792C22}</c15:txfldGUID>
                       <c15:f>'C06F'!$AD$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19172,7 +19172,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000059-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{00000059-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19182,7 +19182,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005A-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000005A-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19192,7 +19192,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005B-9759-48B7-BA79-3459BD31F5C4}"/>
+                  <c16:uniqueId val="{0000005B-CEC7-4370-A398-389D1CDAFA69}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19373,7 +19373,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000047-9759-48B7-BA79-3459BD31F5C4}"/>
+              <c16:uniqueId val="{00000047-CEC7-4370-A398-389D1CDAFA69}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19387,11 +19387,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="889690735"/>
-        <c:axId val="1419250575"/>
+        <c:axId val="1212143552"/>
+        <c:axId val="1098052880"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="889690735"/>
+        <c:axId val="1212143552"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -19415,7 +19415,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419250575"/>
+        <c:crossAx val="1098052880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19423,7 +19423,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419250575"/>
+        <c:axId val="1098052880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0254537518168634"/>
@@ -19457,7 +19457,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="889690735"/>
+        <c:crossAx val="1212143552"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19729,7 +19729,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-B713-4086-A2CA-440DE6CC548C}"/>
+              <c16:uniqueId val="{00000007-E98A-4FDB-86C7-2C37047FE5D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19763,7 +19763,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000009-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19773,7 +19773,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000A-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19801,7 +19801,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B3CABC27-757D-4F42-9C66-55746BCC618A}</c15:txfldGUID>
+                      <c15:txfldGUID>{4A076A65-8A62-4C67-B59D-5C679749886D}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19814,7 +19814,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000B-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19842,7 +19842,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9479504E-3D75-4BEB-941B-90B62F54BB8D}</c15:txfldGUID>
+                      <c15:txfldGUID>{87514F36-57BE-4926-9386-1DDBE7DDF5DF}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19855,7 +19855,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000C-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19883,7 +19883,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E27A4C10-1EBD-46E6-AE97-FB71050F9A66}</c15:txfldGUID>
+                      <c15:txfldGUID>{8833B996-56DB-489E-BABF-674943EDA85B}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19896,7 +19896,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000D-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19924,7 +19924,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4A0A7CC0-F5A3-4B9F-AEC1-7B10F8507465}</c15:txfldGUID>
+                      <c15:txfldGUID>{F0F9B9BC-18A3-4501-87BF-F931827362E4}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -19937,7 +19937,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000E-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19947,7 +19947,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000000F-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19957,7 +19957,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000010-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19967,7 +19967,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000011-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19977,7 +19977,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000012-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19987,7 +19987,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000013-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19997,7 +19997,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000014-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20007,7 +20007,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000015-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20017,7 +20017,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000016-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20027,7 +20027,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000017-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20037,7 +20037,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000018-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20065,7 +20065,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{19E52100-C3F8-435B-9413-696E14036175}</c15:txfldGUID>
+                      <c15:txfldGUID>{2979CF8B-C2DD-4AE0-8B24-8C1E31696ED9}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20078,7 +20078,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000019-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20088,7 +20088,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000001A-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20098,7 +20098,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000001B-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20126,7 +20126,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{27C48E02-AAFA-4B3F-967E-DEAC3B6C651E}</c15:txfldGUID>
+                      <c15:txfldGUID>{8D223A4C-F55A-4DB7-8C90-19114ADF48DD}</c15:txfldGUID>
                       <c15:f>'C06F'!$AG$30</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20139,7 +20139,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000001C-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20320,7 +20320,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-B713-4086-A2CA-440DE6CC548C}"/>
+              <c16:uniqueId val="{00000008-E98A-4FDB-86C7-2C37047FE5D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -20354,7 +20354,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000001E-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20364,7 +20364,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000001F-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20374,7 +20374,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000020-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20384,7 +20384,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000021-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20394,7 +20394,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000022-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20404,7 +20404,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000023-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20432,7 +20432,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2A7F31A8-65E2-4313-A428-DC24A693BCB2}</c15:txfldGUID>
+                      <c15:txfldGUID>{DC840592-CDAC-474B-96A8-F5010FD87051}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20445,7 +20445,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000024-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20473,7 +20473,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8B0C40F3-8D02-4AE2-A00E-64F9447ABD1F}</c15:txfldGUID>
+                      <c15:txfldGUID>{CF34128C-1DDB-454C-8036-4488D43440D9}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20486,7 +20486,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000025-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20514,7 +20514,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{FB0E4579-BCC1-4928-A274-AF3D4F26AA83}</c15:txfldGUID>
+                      <c15:txfldGUID>{BF9D77BD-6BB8-4064-8FDC-7EB2B7551594}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20527,7 +20527,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000026-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20555,7 +20555,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E934C7E2-4116-4AE9-BD1E-AD6F77B7ABCF}</c15:txfldGUID>
+                      <c15:txfldGUID>{E2DD8812-D1F1-4E63-BF0C-04CE1E7188F0}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20568,7 +20568,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000027-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20596,7 +20596,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{673771AC-6DB3-4CD0-A83E-F1879C571D8B}</c15:txfldGUID>
+                      <c15:txfldGUID>{D23B9DF4-8E44-4348-9253-3D32163EE0F3}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20609,7 +20609,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000028-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20637,7 +20637,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9EC60E0E-7370-47B9-A4B8-AFE0F00BF46F}</c15:txfldGUID>
+                      <c15:txfldGUID>{0E4465BB-89B1-404F-95ED-E2E288B13EC7}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20650,7 +20650,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000029-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20678,7 +20678,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ECC515F4-3F4F-4DF7-BD03-43B6E5A6C68C}</c15:txfldGUID>
+                      <c15:txfldGUID>{A8A3851D-C0CD-4106-904D-0FDBEB9BCA1C}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20691,7 +20691,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002A-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20719,7 +20719,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B9A71CD3-F5DD-493E-BD20-07E793A294FA}</c15:txfldGUID>
+                      <c15:txfldGUID>{9C9099F7-48D0-4D62-A030-410429F8CFE1}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20732,7 +20732,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002B-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20760,7 +20760,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{0F1413B3-B3D0-4BB4-BA5E-52BBF9F01851}</c15:txfldGUID>
+                      <c15:txfldGUID>{CE56B1DC-F05A-43DD-90DE-8E9BBF116E2B}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20773,7 +20773,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002C-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20801,7 +20801,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B9C6A79A-F92F-4A7A-915A-6573624CD760}</c15:txfldGUID>
+                      <c15:txfldGUID>{0697487C-7314-46F6-B4B9-BF46D38523BE}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20814,7 +20814,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002D-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20824,7 +20824,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002E-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20834,7 +20834,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{0000002F-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20862,7 +20862,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{51C7B144-0FA6-4477-B666-A97B65520711}</c15:txfldGUID>
+                      <c15:txfldGUID>{EDF26A40-C84D-4DF6-9A6D-3589E26E9A59}</c15:txfldGUID>
                       <c15:f>'C06F'!$AI$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -20875,7 +20875,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000030-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -20885,7 +20885,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-B713-4086-A2CA-440DE6CC548C}"/>
+                  <c16:uniqueId val="{00000031-E98A-4FDB-86C7-2C37047FE5D7}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21066,7 +21066,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-B713-4086-A2CA-440DE6CC548C}"/>
+              <c16:uniqueId val="{0000001D-E98A-4FDB-86C7-2C37047FE5D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -21080,11 +21080,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="890767759"/>
-        <c:axId val="1419126735"/>
+        <c:axId val="1211949472"/>
+        <c:axId val="1097903120"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="890767759"/>
+        <c:axId val="1211949472"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -21101,7 +21101,7 @@
             </a:solidFill>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="1419126735"/>
+        <c:crossAx val="1097903120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -21109,7 +21109,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419126735"/>
+        <c:axId val="1097903120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0254537518168634"/>
@@ -21143,7 +21143,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="890767759"/>
+        <c:crossAx val="1211949472"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21415,7 +21415,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-2514-4504-B84F-766C0A9B4BC5}"/>
+              <c16:uniqueId val="{00000007-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -21467,7 +21467,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D9D7D833-9B5E-48FF-A0B5-0E9F9774CF7A}</c15:txfldGUID>
+                      <c15:txfldGUID>{F6F62E9E-7290-4086-96C7-8087BD9BCFF7}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$11</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21480,7 +21480,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000011-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21508,7 +21508,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{70676A97-3C31-4240-97F5-715709EA0D8D}</c15:txfldGUID>
+                      <c15:txfldGUID>{ED60D257-208D-4DEF-9650-19F560CF9C84}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$12</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21521,7 +21521,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000012-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21549,7 +21549,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8DB5F8E5-9E19-4E3F-BAC4-928B0A693AA4}</c15:txfldGUID>
+                      <c15:txfldGUID>{35961650-7E7F-41B2-BFDF-69D21C429AC0}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$13</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21562,7 +21562,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000013-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21590,7 +21590,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6DB2628C-3EFD-49D7-8891-E5EABBD51DC4}</c15:txfldGUID>
+                      <c15:txfldGUID>{275C0591-9FAC-4C79-B50E-8B0BB54EE9A3}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$14</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21603,7 +21603,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000014-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21631,7 +21631,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5BA5BEFC-55A5-48EC-882B-31AE623C119D}</c15:txfldGUID>
+                      <c15:txfldGUID>{B2E2FE96-3FFB-4757-8BD1-76CF854A83FD}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$15</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21644,7 +21644,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000015-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21672,7 +21672,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5410D011-AD97-49F1-9DDE-35E91B6A6EE3}</c15:txfldGUID>
+                      <c15:txfldGUID>{7AA0D2E2-0FE3-4D05-878D-152335E42424}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$16</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21685,7 +21685,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000016-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21695,7 +21695,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000009-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21705,7 +21705,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000A-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21715,7 +21715,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000B-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21725,7 +21725,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000C-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21735,7 +21735,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000D-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21745,7 +21745,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000E-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21773,7 +21773,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{4904C65F-E755-48AE-9801-F569451DC2EB}</c15:txfldGUID>
+                      <c15:txfldGUID>{FD9F8753-BAAE-475E-90B2-F2D0A816D258}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$23</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21786,7 +21786,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000017-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21814,7 +21814,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{9ECA397C-8738-4376-9A42-A3C04DB898B3}</c15:txfldGUID>
+                      <c15:txfldGUID>{A2ED4E5C-9118-454E-A4FE-DB1C2FA843DA}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$24</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21827,7 +21827,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000018-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21855,7 +21855,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F3D8D035-2638-475C-B502-07C1636F76F8}</c15:txfldGUID>
+                      <c15:txfldGUID>{A068C94E-9B23-4877-9354-EF41940E90F9}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$25</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21868,7 +21868,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000019-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21896,7 +21896,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{2F1E18EA-4519-452C-B4B4-F1D5790013D7}</c15:txfldGUID>
+                      <c15:txfldGUID>{487B1BFE-D3FE-497E-A1C9-E5230C260622}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$26</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21909,7 +21909,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000001A-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21919,7 +21919,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000000F-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21947,7 +21947,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C60D1318-D968-4AC9-B582-85A9F41804E8}</c15:txfldGUID>
+                      <c15:txfldGUID>{53E1F78D-568A-461F-8A12-C88564E10409}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$28</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -21960,7 +21960,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000001B-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21970,7 +21970,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000010-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -21998,7 +21998,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{DAEB0ED1-6255-42B3-BDA0-604AF94EF103}</c15:txfldGUID>
+                      <c15:txfldGUID>{C6EE9C3E-F178-4D0E-80F5-2E9BD5AC7BE7}</c15:txfldGUID>
                       <c15:f>'C12A'!$AG$30</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22011,7 +22011,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000001C-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22195,7 +22195,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-2514-4504-B84F-766C0A9B4BC5}"/>
+              <c16:uniqueId val="{00000008-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -22229,7 +22229,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000001E-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22239,7 +22239,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000001F-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22249,7 +22249,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000020-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22259,7 +22259,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000021-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22269,7 +22269,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000022-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22279,7 +22279,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000023-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22307,7 +22307,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D03429A2-8203-482B-A822-F86CF3375D9F}</c15:txfldGUID>
+                      <c15:txfldGUID>{496549C1-1AE1-4DDF-9065-0E1FC80EC178}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$17</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22320,7 +22320,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002A-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22348,7 +22348,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{75D48B20-DA7A-427C-81DE-F6BA08251AD9}</c15:txfldGUID>
+                      <c15:txfldGUID>{C706D972-5095-4563-8828-E614FE5780B5}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$18</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22361,7 +22361,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002B-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22389,7 +22389,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5F3A71D6-C643-41F4-B442-52B775896ACD}</c15:txfldGUID>
+                      <c15:txfldGUID>{610E598D-2470-40B6-A48D-8FD233836CA3}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$19</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22402,7 +22402,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002C-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22430,7 +22430,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{ED1F632A-5065-4CBE-AF35-497A4D8B572C}</c15:txfldGUID>
+                      <c15:txfldGUID>{6D4BE318-6EBA-4770-9674-6D77335AAB4C}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$20</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22443,7 +22443,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002D-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22471,7 +22471,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B63CD53D-7B53-4041-958E-CA66BC17FF68}</c15:txfldGUID>
+                      <c15:txfldGUID>{442339F1-DE71-44D6-9961-7E13CB2713E8}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$21</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22484,7 +22484,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002E-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22512,7 +22512,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{39922E57-B62D-43F8-9607-CCFDC8E83489}</c15:txfldGUID>
+                      <c15:txfldGUID>{86A3EB9A-4EC1-49C1-97F3-5C1C272D6121}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$22</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22525,7 +22525,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{0000002F-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22535,7 +22535,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000024-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22545,7 +22545,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000025-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22555,7 +22555,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000026-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22565,7 +22565,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000027-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22593,7 +22593,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{16D778F1-08FC-4275-A129-937EE414DD80}</c15:txfldGUID>
+                      <c15:txfldGUID>{00605B9E-7AB4-41FF-883C-BAD29EE95D20}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$27</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22606,7 +22606,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000030-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22616,7 +22616,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000028-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22644,7 +22644,7 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable>
                     <c15:dlblFTEntry>
-                      <c15:txfldGUID>{164752A4-CCB4-489C-96DE-A646F7CD0B35}</c15:txfldGUID>
+                      <c15:txfldGUID>{A7DE38F4-7656-49F5-BDB8-6E9361EC5696}</c15:txfldGUID>
                       <c15:f>'C12A'!$AI$29</c15:f>
                       <c15:dlblFieldTableCache>
                         <c:ptCount val="1"/>
@@ -22657,7 +22657,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000031-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22667,7 +22667,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-2514-4504-B84F-766C0A9B4BC5}"/>
+                  <c16:uniqueId val="{00000029-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -22851,7 +22851,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-2514-4504-B84F-766C0A9B4BC5}"/>
+              <c16:uniqueId val="{0000001D-8F8B-49FA-99F5-FCDA2CEF1B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -22865,11 +22865,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="890762191"/>
-        <c:axId val="1419062415"/>
+        <c:axId val="1211895184"/>
+        <c:axId val="1097880080"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="890762191"/>
+        <c:axId val="1211895184"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -22893,7 +22893,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1419062415"/>
+        <c:crossAx val="1097880080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22901,7 +22901,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1419062415"/>
+        <c:axId val="1097880080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.055607917059378"/>
@@ -22935,7 +22935,7 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
-        <c:crossAx val="890762191"/>
+        <c:crossAx val="1211895184"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23029,7 +23029,7 @@
         <xdr:cNvPr id="2" name="panel_area">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD0C3205-856C-5496-DFFE-028B4C458278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A5F5454-CB97-F8D7-938E-7B0BE56803A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23065,7 +23065,7 @@
         <xdr:cNvPr id="3" name="title_C01A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A8DA807-FDE5-C693-FEC7-6279D58F4CBF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2794C8B7-A757-3013-4542-F6B062B5D7D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23122,7 +23122,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{A41AECA1-8C6E-4908-B2B2-D79C9E751D09}" type="TxLink">
+          <a:fld id="{232CD40E-BA7D-43B6-97E7-7F7B0D42081C}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23158,7 +23158,7 @@
         <xdr:cNvPr id="4" name="title_C01A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E8725F-AB00-C8AF-B904-EEA4B6F13A0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A72773AD-505A-3D31-20A5-98D79F7D7377}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23215,7 +23215,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{79321A8F-4E49-43D3-9093-7A56D25525E8}" type="TxLink">
+          <a:fld id="{C8BA79CE-502F-40AE-B271-6F49CAF478D9}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -23251,7 +23251,7 @@
         <xdr:cNvPr id="5" name="title_C01A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A47CA2-702F-F8B7-B395-221DB2FD6E01}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D7C80A2-F529-32FC-8A5E-802F4634150E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23308,7 +23308,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{3C4B416C-8057-41E9-B409-81464EA204B1}" type="TxLink">
+          <a:fld id="{F67542E3-6F9E-4A2C-B53D-958A567957C3}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23344,7 +23344,7 @@
         <xdr:cNvPr id="6" name="title_C01A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5EF65A0-D292-E0C7-D847-C2EA685AA350}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EFC5739-B52E-ACA7-6302-F0C0D61877B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23401,7 +23401,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{FA8FBDCA-F0D9-4BF1-8FDB-FC48498EDA98}" type="TxLink">
+          <a:fld id="{EF160EFD-5F73-484C-8CD2-638985FED37E}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23442,7 +23442,7 @@
         <xdr:cNvPr id="2" name="panel_channel">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{596724D5-655B-EFBF-B2C5-6C0FFC9AC32B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85202108-391B-74E7-B0AE-876E8560F9D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23478,7 +23478,7 @@
         <xdr:cNvPr id="3" name="title_C02A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA4CFD0-AE0E-B6A4-3854-44DC5BAC3367}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC9B97A2-8C1D-8CBA-3321-0C8262B7F512}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23535,7 +23535,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{061BC67F-262C-4C88-94C1-0A8AD2FC68A9}" type="TxLink">
+          <a:fld id="{5EC310A3-A7FD-4E12-9610-D083A80EBA14}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23571,7 +23571,7 @@
         <xdr:cNvPr id="4" name="title_C02A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E10364-7E8D-A2C6-8C30-AD37254756E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8550E5A-FAEF-20C5-570E-504FB4BFDE18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23628,7 +23628,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{57CEB85C-2ECA-4A6B-A217-39F7BEB2E34F}" type="TxLink">
+          <a:fld id="{83E2E1CA-DF3E-4D2A-AE0E-68F625C6D62F}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -23664,7 +23664,7 @@
         <xdr:cNvPr id="5" name="title_C02A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABB8A95D-ADE2-6B8C-1A13-B11FF254DACE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE8A9A7F-B6F2-9712-F8A5-C3F32AFBB32C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23721,7 +23721,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{8231EE9D-E4BD-4E36-BBB1-99F90DC5D84B}" type="TxLink">
+          <a:fld id="{FA6C7F38-E7FE-4083-8005-708FEFAE63D7}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23757,7 +23757,7 @@
         <xdr:cNvPr id="6" name="title_C02A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{329C9DD3-948D-01AC-9D2C-C7B2489694C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25D8BA8F-88F6-1DBA-F6F9-AA295A6621E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23814,7 +23814,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{EC19425D-2D6D-486A-BAC3-4865762E0642}" type="TxLink">
+          <a:fld id="{33A2019A-99CA-49E5-9AD8-880521A81C78}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23855,7 +23855,7 @@
         <xdr:cNvPr id="2" name="title_C03A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2905024-160D-B0D3-2C16-9853BDFB264D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4209C2A-89A4-7A11-1D6C-B9DFF004911B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23912,7 +23912,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{574EBD35-9E40-4812-97DC-BBAD62FD4D07}" type="TxLink">
+          <a:fld id="{D47BD03E-7EDC-4075-ACD9-3E83B5E5DDF9}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -23948,7 +23948,7 @@
         <xdr:cNvPr id="3" name="title_C03A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D555708F-0995-9D68-F659-B85483AFAEC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5EC2670-C9C3-D00C-1077-4FE11D2E99A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24005,7 +24005,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{A2F2D61F-33FE-48E6-A13E-30941D48D83C}" type="TxLink">
+          <a:fld id="{066C405C-1F7D-4F59-88E0-052E07C88765}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24041,7 +24041,7 @@
         <xdr:cNvPr id="4" name="title_C03A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BC3087B-4DE4-062B-665E-DB07253BFB1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35A9546-D619-88E8-7CD0-24DFF94E8706}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24098,7 +24098,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{8ECE5426-BD8D-4938-8DD0-6709FCF0186B}" type="TxLink">
+          <a:fld id="{4411974E-66C3-4C2F-AC31-CF5A53F28E3C}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24134,7 +24134,7 @@
         <xdr:cNvPr id="5" name="title_C03A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BBE045E-3F89-659B-F170-945E32EFD589}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38A6EE27-4388-4934-ED49-6503C625C3B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24191,7 +24191,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{030D379F-B41D-49D0-BE34-E64C6D56DB0A}" type="TxLink">
+          <a:fld id="{BF16C40B-8892-4A4D-B11A-79469E10D284}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24227,7 +24227,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FCE48D2-EA5D-45E9-F8CB-B524E68A53AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8B8C2F0-899E-2E38-658F-CF8D90CB66F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24268,7 +24268,7 @@
         <xdr:cNvPr id="2" name="title_C04A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE1A8968-5526-9737-3684-D31AA9BE72BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02BBC3C9-FFCC-EEE4-AF79-F682F76FB5D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24325,7 +24325,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{ABFC91DA-CF09-43DD-9255-EF6E110E36CB}" type="TxLink">
+          <a:fld id="{9CC4B480-3573-4149-BDCA-289EB3A02623}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24361,7 +24361,7 @@
         <xdr:cNvPr id="3" name="title_C04A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F50A1DA-E084-C91C-347A-265288E26AD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F57535C4-172C-BE97-2710-6BDCD1FBFE9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24418,7 +24418,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{6AF4851E-D7CC-4A99-86A6-5104BDBF5F9B}" type="TxLink">
+          <a:fld id="{04C62395-47B7-4871-AA47-0D91A60B955D}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24454,7 +24454,7 @@
         <xdr:cNvPr id="4" name="title_C04A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE104D39-B6F6-6702-06D6-2C8F750C1424}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4349D655-B6EC-98DA-72F0-694AD5641A54}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24511,7 +24511,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{A276BE45-81A5-44AE-BB47-9689950971F7}" type="TxLink">
+          <a:fld id="{BF688C13-8F22-457D-A436-A3B2EAAC7964}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24547,7 +24547,7 @@
         <xdr:cNvPr id="5" name="title_C04A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43FE3DF4-04F3-4D16-886B-FE2807890BEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC68D2E8-7B94-9983-EC69-9AA03117835D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24604,7 +24604,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{B1DB1B11-54AD-4C8E-A59F-D43A17072C0E}" type="TxLink">
+          <a:fld id="{812E6B0C-FFB2-4407-8144-7F6B94CF85B7}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24640,7 +24640,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EA7C1CA-D7C1-7DA1-D10F-B452993EFEA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BD6ACB4-892D-0614-A9CF-3E73931ABB7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24681,7 +24681,7 @@
         <xdr:cNvPr id="2" name="title_C05X_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65E26B05-D997-D5AF-51A6-B57A6D9C8866}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E02B94A-C874-99D9-97FC-1E7CDBB87497}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24738,7 +24738,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{221AA859-74A4-49D6-A25C-E7ED7A276DE9}" type="TxLink">
+          <a:fld id="{DEF34653-D331-4DCA-83C8-70605B299392}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24774,7 +24774,7 @@
         <xdr:cNvPr id="3" name="title_C05X_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC4EE25A-6D3E-4F3D-29A1-EABE18E8FDBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE99ECB-4911-C21A-C9CD-63C91930C281}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24831,7 +24831,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{9CAF7A32-04F6-4495-8E08-6C20A198D19D}" type="TxLink">
+          <a:fld id="{1B7EAE36-538E-46AA-B4AA-79B5DD2D11A2}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24867,7 +24867,7 @@
         <xdr:cNvPr id="4" name="title_C05X_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53DD3D8A-4D33-2514-D2D8-AC06EFBFB89A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52FB9425-B551-2ABB-537C-193E91CEFBA7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24924,7 +24924,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{8E1C0CFC-C63F-41C2-8537-A7BEC5BDA2CC}" type="TxLink">
+          <a:fld id="{749858B1-E1F8-4526-B564-F10F07B33E4D}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -24960,7 +24960,7 @@
         <xdr:cNvPr id="5" name="title_C05X_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC81244-86F1-E900-3701-855088BD95BD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A225387B-84B3-EC7B-AA98-1EA14F2F31C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25017,7 +25017,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{A7D2DA5F-94DA-480E-84A7-64791E30827A}" type="TxLink">
+          <a:fld id="{1F225847-64D8-42F2-A9E9-CD87F3DAD9C9}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25053,7 +25053,7 @@
         <xdr:cNvPr id="6" name="tier_wf">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B72AABD-0FB0-68D2-E4C7-30FEF195608F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D421E84D-811F-B4C8-1DCC-F4526E9EA350}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25089,7 +25089,7 @@
         <xdr:cNvPr id="7" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8F9DDD5-B4CB-7D3A-451F-9A0125B80B0D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B8AE6D-4F51-24B1-2793-0CA80AEF1681}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25125,7 +25125,7 @@
         <xdr:cNvPr id="8" name="rule_wf_0">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C28E4B15-B59F-2693-7827-D04A3A5B96D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C61B24E6-7396-6523-CE5F-9A877ADCA3B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25180,7 +25180,7 @@
         <xdr:cNvPr id="9" name="rule_wf_1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D6424FD-45D8-2D39-9A15-11594283D23A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61ED5B10-890F-B781-6913-6AB99A67FE21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25240,7 +25240,7 @@
         <xdr:cNvPr id="2" name="title_C06F_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{283E2CF7-991B-CF60-7302-C28F5A347FEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4B04303-2135-1873-A8A5-83D9A91E2E42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25297,7 +25297,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{67C000F8-2773-417E-8D78-1358508FE81D}" type="TxLink">
+          <a:fld id="{CC66A636-2144-44EF-B47B-0CEA6C1E1B6E}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25333,7 +25333,7 @@
         <xdr:cNvPr id="3" name="title_C06F_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABD7695A-E6F8-FC60-3150-706B2610B8D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EEDCB69-C600-56D3-D06C-20F628833490}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25390,7 +25390,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{D8DB3FD5-D797-41F1-A446-CB370C1618BD}" type="TxLink">
+          <a:fld id="{145A597F-DA73-46AA-BDB9-AA4EC6CE0A01}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25426,7 +25426,7 @@
         <xdr:cNvPr id="4" name="title_C06F_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC34BD2F-DA5F-86A3-2636-87C0DAFEF7E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E42D241-BA04-E106-551E-188113627D22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25483,7 +25483,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{D87E0858-27A2-4852-B401-CCF326C56680}" type="TxLink">
+          <a:fld id="{F40A6820-07F1-41B5-AEFB-5E65BFEE65C6}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25519,7 +25519,7 @@
         <xdr:cNvPr id="5" name="title_C06F_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A812B2B-FD83-9C71-338D-4C4B11CE339D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41CB6235-DCD7-5C87-CFEE-82AB4BD1C037}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25576,7 +25576,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{AC046C58-CC81-410C-BF43-742763FB06EA}" type="TxLink">
+          <a:fld id="{FDD725A2-7D81-460B-886F-415337A64C7A}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25612,7 +25612,7 @@
         <xdr:cNvPr id="6" name="tier_measure">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100F2320-8CB3-B632-2D1B-4BE201718608}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCD752B2-A078-E7B4-B1D2-8039B66CD5DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25648,7 +25648,7 @@
         <xdr:cNvPr id="7" name="tier_wf">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F52A6CA4-A5E6-F24B-CCDB-53E8B368397C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAF6BA13-BAFD-A4CA-45E4-3BFE23533DEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25689,7 +25689,7 @@
         <xdr:cNvPr id="2" name="title_C12A_entity">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4671979-1AD3-F1DA-D6DD-46E8DC1567A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4AC8DB-90E5-2E8D-55F0-10006288F4C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25746,7 +25746,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{6FD3A9FA-EFB0-45BA-81E1-E027E03A7122}" type="TxLink">
+          <a:fld id="{9AE059B1-49EE-42AF-AE80-C8D88934FCA6}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25782,7 +25782,7 @@
         <xdr:cNvPr id="3" name="title_C12A_subject">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCEC1878-AAF8-1E82-696B-5A126AFE926F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{681BEC1F-565B-1306-2680-B00D518B8DCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25839,7 +25839,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{0DB768DB-2B7E-4010-929A-2F4C563213F3}" type="TxLink">
+          <a:fld id="{ECE0B744-31BF-47B8-8DAA-9228DD3BC0EA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25875,7 +25875,7 @@
         <xdr:cNvPr id="4" name="title_C12A_period">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F17E0718-1DE0-8449-BFC9-4DA3B5244E4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{852B4545-7CC3-8023-4B38-3E9B638907DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25932,7 +25932,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{02F673E2-7E05-42D3-A36E-DCE5C4125C5E}" type="TxLink">
+          <a:fld id="{E9491CFF-8500-4FF1-8360-2847DFA97D39}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -25968,7 +25968,7 @@
         <xdr:cNvPr id="5" name="title_C12A_message">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7A665C-638F-B12A-156F-D4F5658465DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51833091-77D7-B7BC-751F-EE26429CC352}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26025,7 +26025,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:fld id="{1954F981-7001-45B2-96E2-7A9A50EC318B}" type="TxLink">
+          <a:fld id="{83EE49F0-F179-4880-A207-F04ED513349B}" type="TxLink">
             <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -26061,7 +26061,7 @@
         <xdr:cNvPr id="6" name="tier_wf_ac">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6D702B-5BAE-B646-C0F7-AEF65F8EF3AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F56EE9EA-AF24-8399-6F31-43BB2AB4F9EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26398,7 +26398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C74142-E4DF-412E-A82F-FC10C8477D5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA385EC-5677-4789-A483-3824963F5EEC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26500,7 +26500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E447FC3-F998-42D9-A926-DFCC7D7BBEF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED367550-A5B5-4F54-B8EF-D697E3235D48}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26985,7 +26985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C7598B-9585-4C41-93BB-6D1709A2A352}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A257669-FDB3-474D-8BCE-A67A7FEF1437}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -28100,7 +28100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448E549B-6B5A-429E-811B-C2AC70EB759E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8F604D-B5AB-4353-A735-EDEAA83BD555}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29777,7 +29777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14895338-4F43-4323-9471-41916537F0B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2C2822-0BDC-415B-92ED-C35B04497D6C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -31864,7 +31864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D3F1E4-B40C-4FBA-8B3E-82D22116F47D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D80E45-1DD8-4A39-8F38-6C00BE03C8D2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -35457,7 +35457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7BBA41-93AC-4869-A337-168433A0D0BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB9F503-8F2C-48AA-813B-9DA482C113A0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -38853,7 +38853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489E1373-634D-4C17-8F3B-E1AFC77437B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267646CA-DBF5-42CD-A233-6CF85D175D6E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
